--- a/dataset/combined_goldset.xlsx
+++ b/dataset/combined_goldset.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -557,11 +557,15 @@
       <c r="L2" t="n">
         <v>43</v>
       </c>
-      <c r="M2" t="n">
-        <v>628108904</v>
-      </c>
-      <c r="N2" t="n">
-        <v>28620242</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>628108904</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>28620242</t>
+        </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,11 +625,15 @@
       <c r="L3" t="n">
         <v>79</v>
       </c>
-      <c r="M3" t="n">
-        <v>26069105</v>
-      </c>
-      <c r="N3" t="n">
-        <v>8774279</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>26069105</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>8774279</t>
+        </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -685,11 +693,15 @@
       <c r="L4" t="n">
         <v>97</v>
       </c>
-      <c r="M4" t="n">
-        <v>33069338</v>
-      </c>
-      <c r="N4" t="n">
-        <v>11720881</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>33069338</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>11720881</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -749,11 +761,15 @@
       <c r="L5" t="n">
         <v>105</v>
       </c>
-      <c r="M5" t="n">
-        <v>46294682</v>
-      </c>
-      <c r="N5" t="n">
-        <v>17311509</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>46294682</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>17311509</t>
+        </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -813,11 +829,15 @@
       <c r="L6" t="n">
         <v>179</v>
       </c>
-      <c r="M6" t="n">
-        <v>358253550</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20016048</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>358253550</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>20016048</t>
+        </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -877,11 +897,15 @@
       <c r="L7" t="n">
         <v>51</v>
       </c>
-      <c r="M7" t="n">
-        <v>373594692</v>
-      </c>
-      <c r="N7" t="n">
-        <v>24965976</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>373594692</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>24965976</t>
+        </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -941,11 +965,15 @@
       <c r="L8" t="n">
         <v>87</v>
       </c>
-      <c r="M8" t="n">
-        <v>372725556</v>
-      </c>
-      <c r="N8" t="n">
-        <v>24534279</v>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>372725556</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>24534279</t>
+        </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1005,11 +1033,15 @@
       <c r="L9" t="n">
         <v>70</v>
       </c>
-      <c r="M9" t="n">
-        <v>606233093</v>
-      </c>
-      <c r="N9" t="n">
-        <v>26190534</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>606233093</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>26190534</t>
+        </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1069,11 +1101,15 @@
       <c r="L10" t="n">
         <v>31</v>
       </c>
-      <c r="M10" t="n">
-        <v>611287283</v>
-      </c>
-      <c r="N10" t="n">
-        <v>27426018</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>611287283</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>27426018</t>
+        </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1133,11 +1169,15 @@
       <c r="L11" t="n">
         <v>125</v>
       </c>
-      <c r="M11" t="n">
-        <v>617090389</v>
-      </c>
-      <c r="N11" t="n">
-        <v>28575537</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>617090389</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>28575537</t>
+        </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1197,11 +1237,15 @@
       <c r="L12" t="n">
         <v>70</v>
       </c>
-      <c r="M12" t="n">
-        <v>46040625</v>
-      </c>
-      <c r="N12" t="n">
-        <v>17132756</v>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>46040625</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>17132756</t>
+        </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1261,11 +1305,15 @@
       <c r="L13" t="n">
         <v>54</v>
       </c>
-      <c r="M13" t="n">
-        <v>369067991</v>
-      </c>
-      <c r="N13" t="n">
-        <v>23557988</v>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>369067991</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>23557988</t>
+        </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1325,11 +1373,15 @@
       <c r="L14" t="n">
         <v>110</v>
       </c>
-      <c r="M14" t="n">
-        <v>372725550</v>
-      </c>
-      <c r="N14" t="n">
-        <v>24534277</v>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>372725550</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>24534277</t>
+        </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1389,11 +1441,15 @@
       <c r="L15" t="n">
         <v>54</v>
       </c>
-      <c r="M15" t="n">
-        <v>608906802</v>
-      </c>
-      <c r="N15" t="n">
-        <v>26890011</v>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>608906802</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>26890011</t>
+        </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1453,11 +1509,15 @@
       <c r="L16" t="n">
         <v>64</v>
       </c>
-      <c r="M16" t="n">
-        <v>602103571</v>
-      </c>
-      <c r="N16" t="n">
-        <v>25036408</v>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>602103571</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>25036408</t>
+        </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1522,8 +1582,10 @@
         <v>47</v>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>26566413</v>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>26566413</t>
+        </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1583,11 +1645,15 @@
       <c r="L18" t="n">
         <v>62</v>
       </c>
-      <c r="M18" t="n">
-        <v>613755495</v>
-      </c>
-      <c r="N18" t="n">
-        <v>27805276</v>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>613755495</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>27805276</t>
+        </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1647,11 +1713,15 @@
       <c r="L19" t="n">
         <v>109</v>
       </c>
-      <c r="M19" t="n">
-        <v>606534920</v>
-      </c>
-      <c r="N19" t="n">
-        <v>26408006</v>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>606534920</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>26408006</t>
+        </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1711,11 +1781,15 @@
       <c r="L20" t="n">
         <v>87</v>
       </c>
-      <c r="M20" t="n">
-        <v>613973505</v>
-      </c>
-      <c r="N20" t="n">
-        <v>27998701</v>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>613973505</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>27998701</t>
+        </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1775,11 +1849,15 @@
       <c r="L21" t="n">
         <v>96</v>
       </c>
-      <c r="M21" t="n">
-        <v>618009047</v>
-      </c>
-      <c r="N21" t="n">
-        <v>28854584</v>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>618009047</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>28854584</t>
+        </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1839,11 +1917,15 @@
       <c r="L22" t="n">
         <v>119</v>
       </c>
-      <c r="M22" t="n">
-        <v>51408406</v>
-      </c>
-      <c r="N22" t="n">
-        <v>21549367</v>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>51408406</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>21549367</t>
+        </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1903,11 +1985,15 @@
       <c r="L23" t="n">
         <v>78</v>
       </c>
-      <c r="M23" t="n">
-        <v>616585534</v>
-      </c>
-      <c r="N23" t="n">
-        <v>28381699</v>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>616585534</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>28381699</t>
+        </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1967,11 +2053,15 @@
       <c r="L24" t="n">
         <v>54</v>
       </c>
-      <c r="M24" t="n">
-        <v>618948888</v>
-      </c>
-      <c r="N24" t="n">
-        <v>29079276</v>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>618948888</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>29079276</t>
+        </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2031,11 +2121,15 @@
       <c r="L25" t="n">
         <v>91</v>
       </c>
-      <c r="M25" t="n">
-        <v>617673786</v>
-      </c>
-      <c r="N25" t="n">
-        <v>28681949</v>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>617673786</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>28681949</t>
+        </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2095,11 +2189,15 @@
       <c r="L26" t="n">
         <v>42</v>
       </c>
-      <c r="M26" t="n">
-        <v>611081096</v>
-      </c>
-      <c r="N26" t="n">
-        <v>27173790</v>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>611081096</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>27173790</t>
+        </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2159,11 +2257,15 @@
       <c r="L27" t="n">
         <v>66</v>
       </c>
-      <c r="M27" t="n">
-        <v>617469113</v>
-      </c>
-      <c r="N27" t="n">
-        <v>27899014</v>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>617469113</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>27899014</t>
+        </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2223,11 +2325,15 @@
       <c r="L28" t="n">
         <v>70</v>
       </c>
-      <c r="M28" t="n">
-        <v>606233093</v>
-      </c>
-      <c r="N28" t="n">
-        <v>26190534</v>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>606233093</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>26190534</t>
+        </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2287,11 +2393,15 @@
       <c r="L29" t="n">
         <v>147</v>
       </c>
-      <c r="M29" t="n">
-        <v>600579322</v>
-      </c>
-      <c r="N29" t="n">
-        <v>25359859</v>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>600579322</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>25359859</t>
+        </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2351,11 +2461,15 @@
       <c r="L30" t="n">
         <v>289</v>
       </c>
-      <c r="M30" t="n">
-        <v>30192723</v>
-      </c>
-      <c r="N30" t="n">
-        <v>10739820</v>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>30192723</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>10739820</t>
+        </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2415,11 +2529,15 @@
       <c r="L31" t="n">
         <v>56</v>
       </c>
-      <c r="M31" t="n">
-        <v>364465314</v>
-      </c>
-      <c r="N31" t="n">
-        <v>22418753</v>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>364465314</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>22418753</t>
+        </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2479,11 +2597,15 @@
       <c r="L32" t="n">
         <v>92</v>
       </c>
-      <c r="M32" t="n">
-        <v>350261213</v>
-      </c>
-      <c r="N32" t="n">
-        <v>18075845</v>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>350261213</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>18075845</t>
+        </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2543,11 +2665,15 @@
       <c r="L33" t="n">
         <v>212</v>
       </c>
-      <c r="M33" t="n">
-        <v>368788596</v>
-      </c>
-      <c r="N33" t="n">
-        <v>23046078</v>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>368788596</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>23046078</t>
+        </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2607,11 +2733,15 @@
       <c r="L34" t="n">
         <v>175</v>
       </c>
-      <c r="M34" t="n">
-        <v>365628102</v>
-      </c>
-      <c r="N34" t="n">
-        <v>22767635</v>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>365628102</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>22767635</t>
+        </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2671,11 +2801,15 @@
       <c r="L35" t="n">
         <v>78</v>
       </c>
-      <c r="M35" t="n">
-        <v>627204979</v>
-      </c>
-      <c r="N35" t="n">
-        <v>30445634</v>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>627204979</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>30445634</t>
+        </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2735,11 +2869,15 @@
       <c r="L36" t="n">
         <v>270</v>
       </c>
-      <c r="M36" t="n">
-        <v>363064566</v>
-      </c>
-      <c r="N36" t="n">
-        <v>21956415</v>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>363064566</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>21956415</t>
+        </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2799,11 +2937,15 @@
       <c r="L37" t="n">
         <v>994</v>
       </c>
-      <c r="M37" t="n">
-        <v>30337085</v>
-      </c>
-      <c r="N37" t="n">
-        <v>10792339</v>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>30337085</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>10792339</t>
+        </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2863,11 +3005,15 @@
       <c r="L38" t="n">
         <v>75</v>
       </c>
-      <c r="M38" t="n">
-        <v>618311573</v>
-      </c>
-      <c r="N38" t="n">
-        <v>29150167</v>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>618311573</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>29150167</t>
+        </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2927,11 +3073,15 @@
       <c r="L39" t="n">
         <v>190</v>
       </c>
-      <c r="M39" t="n">
-        <v>604241881</v>
-      </c>
-      <c r="N39" t="n">
-        <v>25656495</v>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>604241881</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>25656495</t>
+        </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2991,11 +3141,15 @@
       <c r="L40" t="n">
         <v>144</v>
       </c>
-      <c r="M40" t="n">
-        <v>36840951</v>
-      </c>
-      <c r="N40" t="n">
-        <v>12832369</v>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>36840951</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>12832369</t>
+        </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3055,11 +3209,15 @@
       <c r="L41" t="n">
         <v>402</v>
       </c>
-      <c r="M41" t="n">
-        <v>603095200</v>
-      </c>
-      <c r="N41" t="n">
-        <v>25532045</v>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>603095200</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>25532045</t>
+        </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3119,11 +3277,15 @@
       <c r="L42" t="n">
         <v>409</v>
       </c>
-      <c r="M42" t="n">
-        <v>43685413</v>
-      </c>
-      <c r="N42" t="n">
-        <v>16434451</v>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>43685413</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>16434451</t>
+        </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3183,11 +3345,15 @@
       <c r="L43" t="n">
         <v>115</v>
       </c>
-      <c r="M43" t="n">
-        <v>612240128</v>
-      </c>
-      <c r="N43" t="n">
-        <v>27267867</v>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>612240128</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>27267867</t>
+        </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3247,11 +3413,15 @@
       <c r="L44" t="n">
         <v>53</v>
       </c>
-      <c r="M44" t="n">
-        <v>607206258</v>
-      </c>
-      <c r="N44" t="n">
-        <v>26489726</v>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>607206258</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>26489726</t>
+        </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3311,11 +3481,15 @@
       <c r="L45" t="n">
         <v>547</v>
       </c>
-      <c r="M45" t="n">
-        <v>28376967</v>
-      </c>
-      <c r="N45" t="n">
-        <v>9674665</v>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>28376967</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>9674665</t>
+        </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3375,11 +3549,15 @@
       <c r="L46" t="n">
         <v>85</v>
       </c>
-      <c r="M46" t="n">
-        <v>373301644</v>
-      </c>
-      <c r="N46" t="n">
-        <v>24517154</v>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>373301644</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>24517154</t>
+        </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3439,11 +3617,15 @@
       <c r="L47" t="n">
         <v>103</v>
       </c>
-      <c r="M47" t="n">
-        <v>373821401</v>
-      </c>
-      <c r="N47" t="n">
-        <v>24844662</v>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>373821401</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>24844662</t>
+        </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3503,11 +3685,15 @@
       <c r="L48" t="n">
         <v>45</v>
       </c>
-      <c r="M48" t="n">
-        <v>2023887278</v>
-      </c>
-      <c r="N48" t="n">
-        <v>37152875</v>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2023887278</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>37152875</t>
+        </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3567,11 +3753,15 @@
       <c r="L49" t="n">
         <v>118</v>
       </c>
-      <c r="M49" t="n">
-        <v>50182023</v>
-      </c>
-      <c r="N49" t="n">
-        <v>18572014</v>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>50182023</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>18572014</t>
+        </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3631,11 +3821,15 @@
       <c r="L50" t="n">
         <v>37</v>
       </c>
-      <c r="M50" t="n">
-        <v>50393119</v>
-      </c>
-      <c r="N50" t="n">
-        <v>19155002</v>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>50393119</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>19155002</t>
+        </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3695,11 +3889,15 @@
       <c r="L51" t="n">
         <v>181</v>
       </c>
-      <c r="M51" t="n">
-        <v>43466913</v>
-      </c>
-      <c r="N51" t="n">
-        <v>16522285</v>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>43466913</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>16522285</t>
+        </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3759,11 +3957,15 @@
       <c r="L52" t="n">
         <v>59</v>
       </c>
-      <c r="M52" t="n">
-        <v>607207811</v>
-      </c>
-      <c r="N52" t="n">
-        <v>26387977</v>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>607207811</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>26387977</t>
+        </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3823,11 +4025,15 @@
       <c r="L53" t="n">
         <v>95</v>
       </c>
-      <c r="M53" t="n">
-        <v>52989384</v>
-      </c>
-      <c r="N53" t="n">
-        <v>24502891</v>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>52989384</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>24502891</t>
+        </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3887,11 +4093,15 @@
       <c r="L54" t="n">
         <v>32</v>
       </c>
-      <c r="M54" t="n">
-        <v>28239185</v>
-      </c>
-      <c r="N54" t="n">
-        <v>9619535</v>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>28239185</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>9619535</t>
+        </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3951,11 +4161,15 @@
       <c r="L55" t="n">
         <v>289</v>
       </c>
-      <c r="M55" t="n">
-        <v>30192723</v>
-      </c>
-      <c r="N55" t="n">
-        <v>10739820</v>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>30192723</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>10739820</t>
+        </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -4015,11 +4229,15 @@
       <c r="L56" t="n">
         <v>203</v>
       </c>
-      <c r="M56" t="n">
-        <v>40175281</v>
-      </c>
-      <c r="N56" t="n">
-        <v>15638868</v>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>40175281</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>15638868</t>
+        </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -4079,11 +4297,15 @@
       <c r="L57" t="n">
         <v>61</v>
       </c>
-      <c r="M57" t="n">
-        <v>25129865</v>
-      </c>
-      <c r="N57" t="n">
-        <v>7793299</v>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>25129865</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>7793299</t>
+        </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -4143,11 +4365,15 @@
       <c r="L58" t="n">
         <v>369</v>
       </c>
-      <c r="M58" t="n">
-        <v>32751300</v>
-      </c>
-      <c r="N58" t="n">
-        <v>11440917</v>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>32751300</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>11440917</t>
+        </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -4207,11 +4433,15 @@
       <c r="L59" t="n">
         <v>98</v>
       </c>
-      <c r="M59" t="n">
-        <v>352637432</v>
-      </c>
-      <c r="N59" t="n">
-        <v>19013303</v>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>352637432</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>19013303</t>
+        </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4271,11 +4501,15 @@
       <c r="L60" t="n">
         <v>161</v>
       </c>
-      <c r="M60" t="n">
-        <v>38961252</v>
-      </c>
-      <c r="N60" t="n">
-        <v>15279073</v>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>38961252</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>15279073</t>
+        </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4335,11 +4569,15 @@
       <c r="L61" t="n">
         <v>89</v>
       </c>
-      <c r="M61" t="n">
-        <v>50751301</v>
-      </c>
-      <c r="N61" t="n">
-        <v>20413084</v>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>50751301</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>20413084</t>
+        </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4399,11 +4637,15 @@
       <c r="L62" t="n">
         <v>190</v>
       </c>
-      <c r="M62" t="n">
-        <v>604241881</v>
-      </c>
-      <c r="N62" t="n">
-        <v>25656495</v>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>604241881</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>25656495</t>
+        </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4463,11 +4705,15 @@
       <c r="L63" t="n">
         <v>102</v>
       </c>
-      <c r="M63" t="n">
-        <v>361429905</v>
-      </c>
-      <c r="N63" t="n">
-        <v>21114431</v>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>361429905</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>21114431</t>
+        </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4527,11 +4773,15 @@
       <c r="L64" t="n">
         <v>93</v>
       </c>
-      <c r="M64" t="n">
-        <v>51161917</v>
-      </c>
-      <c r="N64" t="n">
-        <v>21083920</v>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>51161917</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>21083920</t>
+        </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4591,11 +4841,15 @@
       <c r="L65" t="n">
         <v>111</v>
       </c>
-      <c r="M65" t="n">
-        <v>361816430</v>
-      </c>
-      <c r="N65" t="n">
-        <v>21427116</v>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>361816430</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>21427116</t>
+        </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4655,11 +4909,15 @@
       <c r="L66" t="n">
         <v>352</v>
       </c>
-      <c r="M66" t="n">
-        <v>41014281</v>
-      </c>
-      <c r="N66" t="n">
-        <v>15797965</v>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>41014281</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>15797965</t>
+        </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4719,11 +4977,15 @@
       <c r="L67" t="n">
         <v>199</v>
       </c>
-      <c r="M67" t="n">
-        <v>43685401</v>
-      </c>
-      <c r="N67" t="n">
-        <v>16449341</v>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>43685401</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>16449341</t>
+        </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4783,11 +5045,15 @@
       <c r="L68" t="n">
         <v>99</v>
       </c>
-      <c r="M68" t="n">
-        <v>362959150</v>
-      </c>
-      <c r="N68" t="n">
-        <v>21937505</v>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>362959150</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>21937505</t>
+        </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4847,11 +5113,15 @@
       <c r="L69" t="n">
         <v>59</v>
       </c>
-      <c r="M69" t="n">
-        <v>52266183</v>
-      </c>
-      <c r="N69" t="n">
-        <v>23089573</v>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>52266183</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>23089573</t>
+        </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4911,11 +5181,15 @@
       <c r="L70" t="n">
         <v>48</v>
       </c>
-      <c r="M70" t="n">
-        <v>365682271</v>
-      </c>
-      <c r="N70" t="n">
-        <v>22497305</v>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>365682271</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>22497305</t>
+        </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4975,11 +5249,15 @@
       <c r="L71" t="n">
         <v>75</v>
       </c>
-      <c r="M71" t="n">
-        <v>50266872</v>
-      </c>
-      <c r="N71" t="n">
-        <v>18722363</v>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>50266872</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>18722363</t>
+        </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -5039,11 +5317,15 @@
       <c r="L72" t="n">
         <v>68</v>
       </c>
-      <c r="M72" t="n">
-        <v>50422765</v>
-      </c>
-      <c r="N72" t="n">
-        <v>19205868</v>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>50422765</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>19205868</t>
+        </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -5103,11 +5385,15 @@
       <c r="L73" t="n">
         <v>72</v>
       </c>
-      <c r="M73" t="n">
-        <v>355293336</v>
-      </c>
-      <c r="N73" t="n">
-        <v>19706563</v>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>355293336</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>19706563</t>
+        </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -5167,11 +5453,15 @@
       <c r="L74" t="n">
         <v>92</v>
       </c>
-      <c r="M74" t="n">
-        <v>52175070</v>
-      </c>
-      <c r="N74" t="n">
-        <v>22921097</v>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>52175070</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>22921097</t>
+        </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -5231,11 +5521,15 @@
       <c r="L75" t="n">
         <v>14</v>
       </c>
-      <c r="M75" t="n">
-        <v>608787090</v>
-      </c>
-      <c r="N75" t="n">
-        <v>26817316</v>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>608787090</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>26817316</t>
+        </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -5295,11 +5589,15 @@
       <c r="L76" t="n">
         <v>99</v>
       </c>
-      <c r="M76" t="n">
-        <v>38951935</v>
-      </c>
-      <c r="N76" t="n">
-        <v>15240646</v>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>38951935</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>15240646</t>
+        </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -5359,11 +5657,15 @@
       <c r="L77" t="n">
         <v>24</v>
       </c>
-      <c r="M77" t="n">
-        <v>26025689</v>
-      </c>
-      <c r="N77" t="n">
-        <v>8706299</v>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>26025689</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>8706299</t>
+        </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -5423,11 +5725,15 @@
       <c r="L78" t="n">
         <v>35</v>
       </c>
-      <c r="M78" t="n">
-        <v>43175617</v>
-      </c>
-      <c r="N78" t="n">
-        <v>16856423</v>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>43175617</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>16856423</t>
+        </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -5487,11 +5793,15 @@
       <c r="L79" t="n">
         <v>81</v>
       </c>
-      <c r="M79" t="n">
-        <v>39330609</v>
-      </c>
-      <c r="N79" t="n">
-        <v>15474880</v>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>39330609</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>15474880</t>
+        </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -5551,11 +5861,15 @@
       <c r="L80" t="n">
         <v>81</v>
       </c>
-      <c r="M80" t="n">
-        <v>604468150</v>
-      </c>
-      <c r="N80" t="n">
-        <v>26015809</v>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>604468150</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>26015809</t>
+        </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -5615,11 +5929,15 @@
       <c r="L81" t="n">
         <v>218</v>
       </c>
-      <c r="M81" t="n">
-        <v>32776544</v>
-      </c>
-      <c r="N81" t="n">
-        <v>11532474</v>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>32776544</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>11532474</t>
+        </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -5679,11 +5997,15 @@
       <c r="L82" t="n">
         <v>82</v>
       </c>
-      <c r="M82" t="n">
-        <v>50712880</v>
-      </c>
-      <c r="N82" t="n">
-        <v>19932893</v>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>50712880</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>19932893</t>
+        </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -5747,11 +6069,15 @@
       <c r="L83" t="n">
         <v>946</v>
       </c>
-      <c r="M83" t="n">
-        <v>40586223</v>
-      </c>
-      <c r="N83" t="n">
-        <v>15623819</v>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>40586223</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>15623819</t>
+        </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -5811,11 +6137,15 @@
       <c r="L84" t="n">
         <v>98</v>
       </c>
-      <c r="M84" t="n">
-        <v>369685010</v>
-      </c>
-      <c r="N84" t="n">
-        <v>23756702</v>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>369685010</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>23756702</t>
+        </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -5875,11 +6205,15 @@
       <c r="L85" t="n">
         <v>34</v>
       </c>
-      <c r="M85" t="n">
-        <v>605888731</v>
-      </c>
-      <c r="N85" t="n">
-        <v>26202923</v>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>605888731</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>26202923</t>
+        </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -5939,11 +6273,15 @@
       <c r="L86" t="n">
         <v>81</v>
       </c>
-      <c r="M86" t="n">
-        <v>51648428</v>
-      </c>
-      <c r="N86" t="n">
-        <v>21982282</v>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>51648428</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>21982282</t>
+        </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -6003,11 +6341,15 @@
       <c r="L87" t="n">
         <v>17</v>
       </c>
-      <c r="M87" t="n">
-        <v>372556357</v>
-      </c>
-      <c r="N87" t="n">
-        <v>24707685</v>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>372556357</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>24707685</t>
+        </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -6067,11 +6409,15 @@
       <c r="L88" t="n">
         <v>55</v>
       </c>
-      <c r="M88" t="n">
-        <v>613562449</v>
-      </c>
-      <c r="N88" t="n">
-        <v>27908217</v>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>613562449</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>27908217</t>
+        </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -6131,11 +6477,15 @@
       <c r="L89" t="n">
         <v>96</v>
       </c>
-      <c r="M89" t="n">
-        <v>614854638</v>
-      </c>
-      <c r="N89" t="n">
-        <v>28280314</v>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>614854638</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>28280314</t>
+        </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -6195,11 +6545,15 @@
       <c r="L90" t="n">
         <v>85</v>
       </c>
-      <c r="M90" t="n">
-        <v>614222549</v>
-      </c>
-      <c r="N90" t="n">
-        <v>28139507</v>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>614222549</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>28139507</t>
+        </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -6259,11 +6613,15 @@
       <c r="L91" t="n">
         <v>105</v>
       </c>
-      <c r="M91" t="n">
-        <v>369455099</v>
-      </c>
-      <c r="N91" t="n">
-        <v>23935436</v>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>369455099</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>23935436</t>
+        </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -6323,11 +6681,15 @@
       <c r="L92" t="n">
         <v>88</v>
       </c>
-      <c r="M92" t="n">
-        <v>605342695</v>
-      </c>
-      <c r="N92" t="n">
-        <v>25138126</v>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>605342695</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>25138126</t>
+        </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -6387,11 +6749,15 @@
       <c r="L93" t="n">
         <v>180</v>
       </c>
-      <c r="M93" t="n">
-        <v>350299801</v>
-      </c>
-      <c r="N93" t="n">
-        <v>17716857</v>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>350299801</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>17716857</t>
+        </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -6451,11 +6817,15 @@
       <c r="L94" t="n">
         <v>96</v>
       </c>
-      <c r="M94" t="n">
-        <v>351807765</v>
-      </c>
-      <c r="N94" t="n">
-        <v>18292843</v>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>351807765</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>18292843</t>
+        </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -6515,11 +6885,15 @@
       <c r="L95" t="n">
         <v>464</v>
       </c>
-      <c r="M95" t="n">
-        <v>38033054</v>
-      </c>
-      <c r="N95" t="n">
-        <v>14671172</v>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>38033054</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>14671172</t>
+        </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -6579,11 +6953,15 @@
       <c r="L96" t="n">
         <v>421</v>
       </c>
-      <c r="M96" t="n">
-        <v>43020236</v>
-      </c>
-      <c r="N96" t="n">
-        <v>16322391</v>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>43020236</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>16322391</t>
+        </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -6643,11 +7021,15 @@
       <c r="L97" t="n">
         <v>107</v>
       </c>
-      <c r="M97" t="n">
-        <v>361110221</v>
-      </c>
-      <c r="N97" t="n">
-        <v>21134104</v>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>361110221</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>21134104</t>
+        </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -6707,11 +7089,15 @@
       <c r="L98" t="n">
         <v>55</v>
       </c>
-      <c r="M98" t="n">
-        <v>613562449</v>
-      </c>
-      <c r="N98" t="n">
-        <v>27908217</v>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>613562449</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>27908217</t>
+        </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -6771,11 +7157,15 @@
       <c r="L99" t="n">
         <v>26</v>
       </c>
-      <c r="M99" t="n">
-        <v>605915046</v>
-      </c>
-      <c r="N99" t="n">
-        <v>25884894</v>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>605915046</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>25884894</t>
+        </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -6835,11 +7225,15 @@
       <c r="L100" t="n">
         <v>83</v>
       </c>
-      <c r="M100" t="n">
-        <v>619113591</v>
-      </c>
-      <c r="N100" t="n">
-        <v>27472811</v>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>619113591</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>27472811</t>
+        </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -6899,11 +7293,15 @@
       <c r="L101" t="n">
         <v>56</v>
       </c>
-      <c r="M101" t="n">
-        <v>611820183</v>
-      </c>
-      <c r="N101" t="n">
-        <v>27648099</v>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>611820183</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>27648099</t>
+        </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -6963,11 +7361,15 @@
       <c r="L102" t="n">
         <v>58</v>
       </c>
-      <c r="M102" t="n">
-        <v>612685871</v>
-      </c>
-      <c r="N102" t="n">
-        <v>27736861</v>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>612685871</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>27736861</t>
+        </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -7027,11 +7429,15 @@
       <c r="L103" t="n">
         <v>185</v>
       </c>
-      <c r="M103" t="n">
-        <v>34596184</v>
-      </c>
-      <c r="N103" t="n">
-        <v>12038887</v>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>34596184</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>12038887</t>
+        </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -7091,11 +7497,15 @@
       <c r="L104" t="n">
         <v>105</v>
       </c>
-      <c r="M104" t="n">
-        <v>369455099</v>
-      </c>
-      <c r="N104" t="n">
-        <v>23935436</v>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>369455099</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>23935436</t>
+        </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -7155,11 +7565,15 @@
       <c r="L105" t="n">
         <v>123</v>
       </c>
-      <c r="M105" t="n">
-        <v>354483145</v>
-      </c>
-      <c r="N105" t="n">
-        <v>19094426</v>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>354483145</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>19094426</t>
+        </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -7219,11 +7633,15 @@
       <c r="L106" t="n">
         <v>10</v>
       </c>
-      <c r="M106" t="n">
-        <v>613807228</v>
-      </c>
-      <c r="N106" t="n">
-        <v>28081337</v>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>613807228</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>28081337</t>
+        </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -7287,8 +7705,10 @@
       <c r="L107" t="n">
         <v>2</v>
       </c>
-      <c r="M107" t="n">
-        <v>600053569</v>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>600053569</t>
+        </is>
       </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
@@ -7354,8 +7774,10 @@
         <v>55</v>
       </c>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" t="n">
-        <v>28360612</v>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>28360612</t>
+        </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -7415,11 +7837,15 @@
       <c r="L109" t="n">
         <v>91</v>
       </c>
-      <c r="M109" t="n">
-        <v>605423053</v>
-      </c>
-      <c r="N109" t="n">
-        <v>26241866</v>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>605423053</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>26241866</t>
+        </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -7479,11 +7905,15 @@
       <c r="L110" t="n">
         <v>51</v>
       </c>
-      <c r="M110" t="n">
-        <v>601071650</v>
-      </c>
-      <c r="N110" t="n">
-        <v>28360650</v>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>601071650</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>28360650</t>
+        </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -7543,11 +7973,15 @@
       <c r="L111" t="n">
         <v>113</v>
       </c>
-      <c r="M111" t="n">
-        <v>361745477</v>
-      </c>
-      <c r="N111" t="n">
-        <v>21473679</v>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>361745477</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>21473679</t>
+        </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -7607,11 +8041,15 @@
       <c r="L112" t="n">
         <v>105</v>
       </c>
-      <c r="M112" t="n">
-        <v>352807288</v>
-      </c>
-      <c r="N112" t="n">
-        <v>19090942</v>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>352807288</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>19090942</t>
+        </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -7671,11 +8109,15 @@
       <c r="L113" t="n">
         <v>187</v>
       </c>
-      <c r="M113" t="n">
-        <v>50390882</v>
-      </c>
-      <c r="N113" t="n">
-        <v>19150179</v>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>50390882</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>19150179</t>
+        </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -7735,11 +8177,15 @@
       <c r="L114" t="n">
         <v>180</v>
       </c>
-      <c r="M114" t="n">
-        <v>350299801</v>
-      </c>
-      <c r="N114" t="n">
-        <v>17716857</v>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>350299801</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>17716857</t>
+        </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -7799,11 +8245,15 @@
       <c r="L115" t="n">
         <v>104</v>
       </c>
-      <c r="M115" t="n">
-        <v>50694356</v>
-      </c>
-      <c r="N115" t="n">
-        <v>19896652</v>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>50694356</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>19896652</t>
+        </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -7863,11 +8313,15 @@
       <c r="L116" t="n">
         <v>203</v>
       </c>
-      <c r="M116" t="n">
-        <v>362918410</v>
-      </c>
-      <c r="N116" t="n">
-        <v>21984577</v>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>362918410</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>21984577</t>
+        </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -7927,11 +8381,15 @@
       <c r="L117" t="n">
         <v>40</v>
       </c>
-      <c r="M117" t="n">
-        <v>373060330</v>
-      </c>
-      <c r="N117" t="n">
-        <v>24658986</v>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>373060330</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>24658986</t>
+        </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -7991,11 +8449,15 @@
       <c r="L118" t="n">
         <v>228</v>
       </c>
-      <c r="M118" t="n">
-        <v>361816434</v>
-      </c>
-      <c r="N118" t="n">
-        <v>21436137</v>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>361816434</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>21436137</t>
+        </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -8055,11 +8517,15 @@
       <c r="L119" t="n">
         <v>464</v>
       </c>
-      <c r="M119" t="n">
-        <v>38033054</v>
-      </c>
-      <c r="N119" t="n">
-        <v>14671172</v>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>38033054</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>14671172</t>
+        </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -8119,11 +8585,15 @@
       <c r="L120" t="n">
         <v>130</v>
       </c>
-      <c r="M120" t="n">
-        <v>369352369</v>
-      </c>
-      <c r="N120" t="n">
-        <v>23407282</v>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>369352369</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>23407282</t>
+        </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -8183,11 +8653,15 @@
       <c r="L121" t="n">
         <v>49</v>
       </c>
-      <c r="M121" t="n">
-        <v>52671693</v>
-      </c>
-      <c r="N121" t="n">
-        <v>23849090</v>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>52671693</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>23849090</t>
+        </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -8247,11 +8721,15 @@
       <c r="L122" t="n">
         <v>421</v>
       </c>
-      <c r="M122" t="n">
-        <v>43020236</v>
-      </c>
-      <c r="N122" t="n">
-        <v>16322391</v>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>43020236</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>16322391</t>
+        </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -8315,8 +8793,10 @@
       <c r="L123" t="n">
         <v>35</v>
       </c>
-      <c r="M123" t="n">
-        <v>369621417</v>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>369621417</t>
+        </is>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
@@ -8377,11 +8857,15 @@
       <c r="L124" t="n">
         <v>275</v>
       </c>
-      <c r="M124" t="n">
-        <v>43875199</v>
-      </c>
-      <c r="N124" t="n">
-        <v>16769740</v>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>43875199</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>16769740</t>
+        </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -8441,11 +8925,15 @@
       <c r="L125" t="n">
         <v>646</v>
       </c>
-      <c r="M125" t="n">
-        <v>46829130</v>
-      </c>
-      <c r="N125" t="n">
-        <v>17397839</v>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>46829130</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>17397839</t>
+        </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -8510,8 +8998,10 @@
         <v>84</v>
       </c>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="n">
-        <v>25722515</v>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>25722515</t>
+        </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -8571,11 +9061,15 @@
       <c r="L127" t="n">
         <v>212</v>
       </c>
-      <c r="M127" t="n">
-        <v>358141838</v>
-      </c>
-      <c r="N127" t="n">
-        <v>19933236</v>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>358141838</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>19933236</t>
+        </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -8635,11 +9129,15 @@
       <c r="L128" t="n">
         <v>36</v>
       </c>
-      <c r="M128" t="n">
-        <v>372460140</v>
-      </c>
-      <c r="N128" t="n">
-        <v>24464003</v>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>372460140</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>24464003</t>
+        </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -8699,11 +9197,15 @@
       <c r="L129" t="n">
         <v>30</v>
       </c>
-      <c r="M129" t="n">
-        <v>610791061</v>
-      </c>
-      <c r="N129" t="n">
-        <v>27377844</v>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>610791061</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>27377844</t>
+        </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -8763,11 +9265,15 @@
       <c r="L130" t="n">
         <v>132</v>
       </c>
-      <c r="M130" t="n">
-        <v>354985951</v>
-      </c>
-      <c r="N130" t="n">
-        <v>19533486</v>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>354985951</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>19533486</t>
+        </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -8827,11 +9333,15 @@
       <c r="L131" t="n">
         <v>133</v>
       </c>
-      <c r="M131" t="n">
-        <v>51226025</v>
-      </c>
-      <c r="N131" t="n">
-        <v>21232840</v>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>51226025</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>21232840</t>
+        </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -8891,11 +9401,15 @@
       <c r="L132" t="n">
         <v>312</v>
       </c>
-      <c r="M132" t="n">
-        <v>50223069</v>
-      </c>
-      <c r="N132" t="n">
-        <v>18672334</v>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>50223069</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>18672334</t>
+        </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -8955,11 +9469,15 @@
       <c r="L133" t="n">
         <v>144</v>
       </c>
-      <c r="M133" t="n">
-        <v>358330456</v>
-      </c>
-      <c r="N133" t="n">
-        <v>20050767</v>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>358330456</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>20050767</t>
+        </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -9019,11 +9537,15 @@
       <c r="L134" t="n">
         <v>123</v>
       </c>
-      <c r="M134" t="n">
-        <v>365185298</v>
-      </c>
-      <c r="N134" t="n">
-        <v>22493025</v>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>365185298</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>22493025</t>
+        </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -9083,11 +9605,15 @@
       <c r="L135" t="n">
         <v>125</v>
       </c>
-      <c r="M135" t="n">
-        <v>604791412</v>
-      </c>
-      <c r="N135" t="n">
-        <v>25432918</v>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>604791412</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>25432918</t>
+        </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -9145,8 +9671,10 @@
       </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
-      <c r="M136" t="n">
-        <v>354694034</v>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>354694034</t>
+        </is>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
@@ -9207,11 +9735,15 @@
       <c r="L137" t="n">
         <v>149</v>
       </c>
-      <c r="M137" t="n">
-        <v>51330337</v>
-      </c>
-      <c r="N137" t="n">
-        <v>21911106</v>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>51330337</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>21911106</t>
+        </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -9271,11 +9803,15 @@
       <c r="L138" t="n">
         <v>63</v>
       </c>
-      <c r="M138" t="n">
-        <v>52607085</v>
-      </c>
-      <c r="N138" t="n">
-        <v>23726743</v>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>52607085</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>23726743</t>
+        </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -9340,8 +9876,10 @@
         <v>70</v>
       </c>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="n">
-        <v>26464839</v>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>26464839</t>
+        </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -9401,11 +9939,15 @@
       <c r="L140" t="n">
         <v>68</v>
       </c>
-      <c r="M140" t="n">
-        <v>51483568</v>
-      </c>
-      <c r="N140" t="n">
-        <v>21688169</v>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>51483568</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>21688169</t>
+        </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -9465,11 +10007,15 @@
       <c r="L141" t="n">
         <v>103</v>
       </c>
-      <c r="M141" t="n">
-        <v>373821401</v>
-      </c>
-      <c r="N141" t="n">
-        <v>24844662</v>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>373821401</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>24844662</t>
+        </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -9529,11 +10075,15 @@
       <c r="L142" t="n">
         <v>53</v>
       </c>
-      <c r="M142" t="n">
-        <v>352718618</v>
-      </c>
-      <c r="N142" t="n">
-        <v>19012100</v>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>352718618</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>19012100</t>
+        </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -9597,8 +10147,10 @@
       <c r="L143" t="n">
         <v>40</v>
       </c>
-      <c r="M143" t="n">
-        <v>358850074</v>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>358850074</t>
+        </is>
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
@@ -9659,11 +10211,15 @@
       <c r="L144" t="n">
         <v>250</v>
       </c>
-      <c r="M144" t="n">
-        <v>38668404</v>
-      </c>
-      <c r="N144" t="n">
-        <v>15184695</v>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>38668404</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>15184695</t>
+        </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -9723,11 +10279,15 @@
       <c r="L145" t="n">
         <v>78</v>
       </c>
-      <c r="M145" t="n">
-        <v>607606742</v>
-      </c>
-      <c r="N145" t="n">
-        <v>24274091</v>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>607606742</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>24274091</t>
+        </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -9787,11 +10347,15 @@
       <c r="L146" t="n">
         <v>161</v>
       </c>
-      <c r="M146" t="n">
-        <v>606879260</v>
-      </c>
-      <c r="N146" t="n">
-        <v>26406234</v>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>606879260</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>26406234</t>
+        </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -9851,11 +10415,15 @@
       <c r="L147" t="n">
         <v>120</v>
       </c>
-      <c r="M147" t="n">
-        <v>354808326</v>
-      </c>
-      <c r="N147" t="n">
-        <v>19204602</v>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>354808326</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>19204602</t>
+        </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -9915,11 +10483,15 @@
       <c r="L148" t="n">
         <v>85</v>
       </c>
-      <c r="M148" t="n">
-        <v>626546590</v>
-      </c>
-      <c r="N148" t="n">
-        <v>29443823</v>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>626546590</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>29443823</t>
+        </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -9979,11 +10551,15 @@
       <c r="L149" t="n">
         <v>259</v>
       </c>
-      <c r="M149" t="n">
-        <v>24114347</v>
-      </c>
-      <c r="N149" t="n">
-        <v>8150098</v>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>24114347</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>8150098</t>
+        </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -10043,11 +10619,15 @@
       <c r="L150" t="n">
         <v>313</v>
       </c>
-      <c r="M150" t="n">
-        <v>39092044</v>
-      </c>
-      <c r="N150" t="n">
-        <v>15302293</v>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>39092044</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>15302293</t>
+        </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -10107,11 +10687,15 @@
       <c r="L151" t="n">
         <v>292</v>
       </c>
-      <c r="M151" t="n">
-        <v>352789525</v>
-      </c>
-      <c r="N151" t="n">
-        <v>18728175</v>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>352789525</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>18728175</t>
+        </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -10171,11 +10755,15 @@
       <c r="L152" t="n">
         <v>236</v>
       </c>
-      <c r="M152" t="n">
-        <v>361024753</v>
-      </c>
-      <c r="N152" t="n">
-        <v>20943753</v>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>361024753</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>20943753</t>
+        </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -10235,11 +10823,15 @@
       <c r="L153" t="n">
         <v>84</v>
       </c>
-      <c r="M153" t="n">
-        <v>601811686</v>
-      </c>
-      <c r="N153" t="n">
-        <v>25545309</v>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>601811686</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>25545309</t>
+        </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -10299,11 +10891,15 @@
       <c r="L154" t="n">
         <v>97</v>
       </c>
-      <c r="M154" t="n">
-        <v>51757308</v>
-      </c>
-      <c r="N154" t="n">
-        <v>22154367</v>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>51757308</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>22154367</t>
+        </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -10363,11 +10959,15 @@
       <c r="L155" t="n">
         <v>116</v>
       </c>
-      <c r="M155" t="n">
-        <v>52634642</v>
-      </c>
-      <c r="N155" t="n">
-        <v>23763822</v>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>52634642</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>23763822</t>
+        </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -10427,11 +11027,15 @@
       <c r="L156" t="n">
         <v>256</v>
       </c>
-      <c r="M156" t="n">
-        <v>355026530</v>
-      </c>
-      <c r="N156" t="n">
-        <v>19494176</v>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>355026530</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>19494176</t>
+        </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -10489,8 +11093,10 @@
       </c>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
-      <c r="M157" t="n">
-        <v>610467126</v>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>610467126</t>
+        </is>
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
@@ -10555,8 +11161,10 @@
       <c r="L158" t="n">
         <v>3</v>
       </c>
-      <c r="M158" t="n">
-        <v>373928478</v>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>373928478</t>
+        </is>
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
@@ -10617,11 +11225,15 @@
       <c r="L159" t="n">
         <v>162</v>
       </c>
-      <c r="M159" t="n">
-        <v>602740228</v>
-      </c>
-      <c r="N159" t="n">
-        <v>25287137</v>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>602740228</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>25287137</t>
+        </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -10686,8 +11298,10 @@
         <v>65</v>
       </c>
       <c r="M160" t="inlineStr"/>
-      <c r="N160" t="n">
-        <v>26311969</v>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>26311969</t>
+        </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -10747,11 +11361,15 @@
       <c r="L161" t="n">
         <v>229</v>
       </c>
-      <c r="M161" t="n">
-        <v>46556413</v>
-      </c>
-      <c r="N161" t="n">
-        <v>17264174</v>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>46556413</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>17264174</t>
+        </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -10811,11 +11429,15 @@
       <c r="L162" t="n">
         <v>156</v>
       </c>
-      <c r="M162" t="n">
-        <v>53208680</v>
-      </c>
-      <c r="N162" t="n">
-        <v>24956415</v>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>53208680</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>24956415</t>
+        </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -10875,11 +11497,15 @@
       <c r="L163" t="n">
         <v>168</v>
       </c>
-      <c r="M163" t="n">
-        <v>600257011</v>
-      </c>
-      <c r="N163" t="n">
-        <v>25194966</v>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>600257011</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>25194966</t>
+        </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -10939,11 +11565,15 @@
       <c r="L164" t="n">
         <v>119</v>
       </c>
-      <c r="M164" t="n">
-        <v>621436826</v>
-      </c>
-      <c r="N164" t="n">
-        <v>28466507</v>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>621436826</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>28466507</t>
+        </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -11003,11 +11633,15 @@
       <c r="L165" t="n">
         <v>93</v>
       </c>
-      <c r="M165" t="n">
-        <v>615419888</v>
-      </c>
-      <c r="N165" t="n">
-        <v>28316072</v>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>615419888</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>28316072</t>
+        </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -11067,11 +11701,15 @@
       <c r="L166" t="n">
         <v>144</v>
       </c>
-      <c r="M166" t="n">
-        <v>52600290</v>
-      </c>
-      <c r="N166" t="n">
-        <v>23444983</v>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>52600290</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>23444983</t>
+        </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -11131,11 +11769,15 @@
       <c r="L167" t="n">
         <v>168</v>
       </c>
-      <c r="M167" t="n">
-        <v>366069558</v>
-      </c>
-      <c r="N167" t="n">
-        <v>22855917</v>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>366069558</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>22855917</t>
+        </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -11195,11 +11837,15 @@
       <c r="L168" t="n">
         <v>566</v>
       </c>
-      <c r="M168" t="n">
-        <v>36207827</v>
-      </c>
-      <c r="N168" t="n">
-        <v>12574218</v>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>36207827</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>12574218</t>
+        </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -11259,11 +11905,15 @@
       <c r="L169" t="n">
         <v>299</v>
       </c>
-      <c r="M169" t="n">
-        <v>38376121</v>
-      </c>
-      <c r="N169" t="n">
-        <v>15037413</v>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>38376121</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>15037413</t>
+        </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -11323,11 +11973,15 @@
       <c r="L170" t="n">
         <v>72</v>
       </c>
-      <c r="M170" t="n">
-        <v>362729810</v>
-      </c>
-      <c r="N170" t="n">
-        <v>21627406</v>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>362729810</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>21627406</t>
+        </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -11387,11 +12041,15 @@
       <c r="L171" t="n">
         <v>72</v>
       </c>
-      <c r="M171" t="n">
-        <v>605084860</v>
-      </c>
-      <c r="N171" t="n">
-        <v>26132306</v>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>605084860</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>26132306</t>
+        </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -11451,11 +12109,15 @@
       <c r="L172" t="n">
         <v>161</v>
       </c>
-      <c r="M172" t="n">
-        <v>606879260</v>
-      </c>
-      <c r="N172" t="n">
-        <v>26406234</v>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>606879260</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>26406234</t>
+        </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -11515,11 +12177,15 @@
       <c r="L173" t="n">
         <v>283</v>
       </c>
-      <c r="M173" t="n">
-        <v>352340724</v>
-      </c>
-      <c r="N173" t="n">
-        <v>18583464</v>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>352340724</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>18583464</t>
+        </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -11579,11 +12245,15 @@
       <c r="L174" t="n">
         <v>67</v>
       </c>
-      <c r="M174" t="n">
-        <v>618848453</v>
-      </c>
-      <c r="N174" t="n">
-        <v>28912358</v>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>618848453</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>28912358</t>
+        </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -11643,11 +12313,15 @@
       <c r="L175" t="n">
         <v>57</v>
       </c>
-      <c r="M175" t="n">
-        <v>600190515</v>
-      </c>
-      <c r="N175" t="n">
-        <v>25473629</v>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>600190515</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>25473629</t>
+        </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -11707,11 +12381,15 @@
       <c r="L176" t="n">
         <v>56</v>
       </c>
-      <c r="M176" t="n">
-        <v>619534286</v>
-      </c>
-      <c r="N176" t="n">
-        <v>29202210</v>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>619534286</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>29202210</t>
+        </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -11771,11 +12449,15 @@
       <c r="L177" t="n">
         <v>80</v>
       </c>
-      <c r="M177" t="n">
-        <v>27344860</v>
-      </c>
-      <c r="N177" t="n">
-        <v>9272421</v>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>27344860</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>9272421</t>
+        </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -11835,11 +12517,15 @@
       <c r="L178" t="n">
         <v>114</v>
       </c>
-      <c r="M178" t="n">
-        <v>29529489</v>
-      </c>
-      <c r="N178" t="n">
-        <v>10526249</v>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>29529489</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>10526249</t>
+        </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -11899,11 +12585,15 @@
       <c r="L179" t="n">
         <v>257</v>
       </c>
-      <c r="M179" t="n">
-        <v>44536872</v>
-      </c>
-      <c r="N179" t="n">
-        <v>16868063</v>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>44536872</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>16868063</t>
+        </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
@@ -11963,11 +12653,15 @@
       <c r="L180" t="n">
         <v>270</v>
       </c>
-      <c r="M180" t="n">
-        <v>38200907</v>
-      </c>
-      <c r="N180" t="n">
-        <v>14725687</v>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>38200907</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>14725687</t>
+        </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -12027,11 +12721,15 @@
       <c r="L181" t="n">
         <v>270</v>
       </c>
-      <c r="M181" t="n">
-        <v>38200907</v>
-      </c>
-      <c r="N181" t="n">
-        <v>14725687</v>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>38200907</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>14725687</t>
+        </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -12091,11 +12789,15 @@
       <c r="L182" t="n">
         <v>198</v>
       </c>
-      <c r="M182" t="n">
-        <v>38766362</v>
-      </c>
-      <c r="N182" t="n">
-        <v>15181054</v>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>38766362</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>15181054</t>
+        </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
@@ -12155,11 +12857,15 @@
       <c r="L183" t="n">
         <v>142</v>
       </c>
-      <c r="M183" t="n">
-        <v>369781027</v>
-      </c>
-      <c r="N183" t="n">
-        <v>23846820</v>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>369781027</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>23846820</t>
+        </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
@@ -12219,11 +12925,15 @@
       <c r="L184" t="n">
         <v>9</v>
       </c>
-      <c r="M184" t="n">
-        <v>607281483</v>
-      </c>
-      <c r="N184" t="n">
-        <v>25330687</v>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>607281483</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>25330687</t>
+        </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -12283,11 +12993,15 @@
       <c r="L185" t="n">
         <v>223</v>
       </c>
-      <c r="M185" t="n">
-        <v>38507907</v>
-      </c>
-      <c r="N185" t="n">
-        <v>15070917</v>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>38507907</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>15070917</t>
+        </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -12347,11 +13061,15 @@
       <c r="L186" t="n">
         <v>76</v>
       </c>
-      <c r="M186" t="n">
-        <v>617330901</v>
-      </c>
-      <c r="N186" t="n">
-        <v>28712591</v>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>617330901</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>28712591</t>
+        </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
@@ -12411,11 +13129,15 @@
       <c r="L187" t="n">
         <v>79</v>
       </c>
-      <c r="M187" t="n">
-        <v>52669706</v>
-      </c>
-      <c r="N187" t="n">
-        <v>23845740</v>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>52669706</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>23845740</t>
+        </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
@@ -12475,11 +13197,15 @@
       <c r="L188" t="n">
         <v>49</v>
       </c>
-      <c r="M188" t="n">
-        <v>608699143</v>
-      </c>
-      <c r="N188" t="n">
-        <v>27904553</v>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>608699143</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>27904553</t>
+        </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
@@ -12539,11 +13265,15 @@
       <c r="L189" t="n">
         <v>197</v>
       </c>
-      <c r="M189" t="n">
-        <v>46354320</v>
-      </c>
-      <c r="N189" t="n">
-        <v>17327307</v>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>46354320</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>17327307</t>
+        </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
@@ -12603,11 +13333,15 @@
       <c r="L190" t="n">
         <v>163</v>
       </c>
-      <c r="M190" t="n">
-        <v>30337084</v>
-      </c>
-      <c r="N190" t="n">
-        <v>10792338</v>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>30337084</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>10792338</t>
+        </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
@@ -12667,11 +13401,15 @@
       <c r="L191" t="n">
         <v>87</v>
       </c>
-      <c r="M191" t="n">
-        <v>30154109</v>
-      </c>
-      <c r="N191" t="n">
-        <v>10731531</v>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>30154109</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>10731531</t>
+        </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
@@ -12731,11 +13469,15 @@
       <c r="L192" t="n">
         <v>72</v>
       </c>
-      <c r="M192" t="n">
-        <v>53015253</v>
-      </c>
-      <c r="N192" t="n">
-        <v>24559619</v>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>53015253</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>24559619</t>
+        </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
@@ -12795,11 +13537,15 @@
       <c r="L193" t="n">
         <v>54</v>
       </c>
-      <c r="M193" t="n">
-        <v>39243207</v>
-      </c>
-      <c r="N193" t="n">
-        <v>15374729</v>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>39243207</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>15374729</t>
+        </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
@@ -12859,11 +13605,15 @@
       <c r="L194" t="n">
         <v>69</v>
       </c>
-      <c r="M194" t="n">
-        <v>51933707</v>
-      </c>
-      <c r="N194" t="n">
-        <v>22464410</v>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>51933707</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>22464410</t>
+        </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -12923,11 +13673,15 @@
       <c r="L195" t="n">
         <v>76</v>
       </c>
-      <c r="M195" t="n">
-        <v>13174422</v>
-      </c>
-      <c r="N195" t="n">
-        <v>7160531</v>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>13174422</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>7160531</t>
+        </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
@@ -12987,11 +13741,15 @@
       <c r="L196" t="n">
         <v>23</v>
       </c>
-      <c r="M196" t="n">
-        <v>20204961</v>
-      </c>
-      <c r="N196" t="n">
-        <v>1973920</v>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>20204961</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>1973920</t>
+        </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
@@ -13051,11 +13809,15 @@
       <c r="L197" t="n">
         <v>50</v>
       </c>
-      <c r="M197" t="n">
-        <v>21290834</v>
-      </c>
-      <c r="N197" t="n">
-        <v>1774730</v>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>21290834</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>1774730</t>
+        </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
@@ -13115,11 +13877,15 @@
       <c r="L198" t="n">
         <v>69</v>
       </c>
-      <c r="M198" t="n">
-        <v>22215535</v>
-      </c>
-      <c r="N198" t="n">
-        <v>1601149</v>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>22215535</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>1601149</t>
+        </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -13179,11 +13945,15 @@
       <c r="L199" t="n">
         <v>146</v>
       </c>
-      <c r="M199" t="n">
-        <v>23324775</v>
-      </c>
-      <c r="N199" t="n">
-        <v>8224271</v>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>23324775</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>8224271</t>
+        </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -13243,11 +14013,15 @@
       <c r="L200" t="n">
         <v>65</v>
       </c>
-      <c r="M200" t="n">
-        <v>27469204</v>
-      </c>
-      <c r="N200" t="n">
-        <v>9360193</v>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>27469204</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>9360193</t>
+        </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -13307,11 +14081,15 @@
       <c r="L201" t="n">
         <v>74</v>
       </c>
-      <c r="M201" t="n">
-        <v>27360575</v>
-      </c>
-      <c r="N201" t="n">
-        <v>9284012</v>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>27360575</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>9284012</t>
+        </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
@@ -13371,11 +14149,15 @@
       <c r="L202" t="n">
         <v>80</v>
       </c>
-      <c r="M202" t="n">
-        <v>29149859</v>
-      </c>
-      <c r="N202" t="n">
-        <v>10464001</v>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>29149859</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>10464001</t>
+        </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -13435,11 +14217,15 @@
       <c r="L203" t="n">
         <v>49</v>
       </c>
-      <c r="M203" t="n">
-        <v>32016799</v>
-      </c>
-      <c r="N203" t="n">
-        <v>11153260</v>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>32016799</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>11153260</t>
+        </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -13499,11 +14285,15 @@
       <c r="L204" t="n">
         <v>80</v>
       </c>
-      <c r="M204" t="n">
-        <v>30153940</v>
-      </c>
-      <c r="N204" t="n">
-        <v>10870780</v>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>30153940</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>10870780</t>
+        </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
@@ -13563,11 +14353,15 @@
       <c r="L205" t="n">
         <v>206</v>
       </c>
-      <c r="M205" t="n">
-        <v>32149412</v>
-      </c>
-      <c r="N205" t="n">
-        <v>11157811</v>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>32149412</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>11157811</t>
+        </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
@@ -13627,11 +14421,15 @@
       <c r="L206" t="n">
         <v>237</v>
       </c>
-      <c r="M206" t="n">
-        <v>34007478</v>
-      </c>
-      <c r="N206" t="n">
-        <v>11726582</v>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>34007478</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>11726582</t>
+        </is>
       </c>
       <c r="O206" t="inlineStr">
         <is>
@@ -13691,11 +14489,15 @@
       <c r="L207" t="n">
         <v>163</v>
       </c>
-      <c r="M207" t="n">
-        <v>36164639</v>
-      </c>
-      <c r="N207" t="n">
-        <v>12566751</v>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>36164639</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>12566751</t>
+        </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
@@ -13755,11 +14557,15 @@
       <c r="L208" t="n">
         <v>440</v>
       </c>
-      <c r="M208" t="n">
-        <v>35174106</v>
-      </c>
-      <c r="N208" t="n">
-        <v>12351531</v>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>35174106</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>12351531</t>
+        </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -13819,11 +14625,15 @@
       <c r="L209" t="n">
         <v>144</v>
       </c>
-      <c r="M209" t="n">
-        <v>36840951</v>
-      </c>
-      <c r="N209" t="n">
-        <v>12832369</v>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>36840951</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>12832369</t>
+        </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -13883,11 +14693,15 @@
       <c r="L210" t="n">
         <v>94</v>
       </c>
-      <c r="M210" t="n">
-        <v>36434298</v>
-      </c>
-      <c r="N210" t="n">
-        <v>12706273</v>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>36434298</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>12706273</t>
+        </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
@@ -13947,11 +14761,15 @@
       <c r="L211" t="n">
         <v>296</v>
       </c>
-      <c r="M211" t="n">
-        <v>38807703</v>
-      </c>
-      <c r="N211" t="n">
-        <v>15117896</v>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>38807703</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>15117896</t>
+        </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -14011,11 +14829,15 @@
       <c r="L212" t="n">
         <v>157</v>
       </c>
-      <c r="M212" t="n">
-        <v>39036995</v>
-      </c>
-      <c r="N212" t="n">
-        <v>15270785</v>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>39036995</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>15270785</t>
+        </is>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -14075,11 +14897,15 @@
       <c r="L213" t="n">
         <v>94</v>
       </c>
-      <c r="M213" t="n">
-        <v>39486899</v>
-      </c>
-      <c r="N213" t="n">
-        <v>15697074</v>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>39486899</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>15697074</t>
+        </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -14139,11 +14965,15 @@
       <c r="L214" t="n">
         <v>251</v>
       </c>
-      <c r="M214" t="n">
-        <v>41418494</v>
-      </c>
-      <c r="N214" t="n">
-        <v>15802312</v>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>41418494</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>15802312</t>
+        </is>
       </c>
       <c r="O214" t="inlineStr">
         <is>
@@ -14203,11 +15033,15 @@
       <c r="L215" t="n">
         <v>45</v>
       </c>
-      <c r="M215" t="n">
-        <v>43530198</v>
-      </c>
-      <c r="N215" t="n">
-        <v>16598331</v>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>43530198</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>16598331</t>
+        </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
@@ -14267,11 +15101,15 @@
       <c r="L216" t="n">
         <v>272</v>
       </c>
-      <c r="M216" t="n">
-        <v>44336846</v>
-      </c>
-      <c r="N216" t="n">
-        <v>16816057</v>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>44336846</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>16816057</t>
+        </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
@@ -14331,11 +15169,15 @@
       <c r="L217" t="n">
         <v>62</v>
       </c>
-      <c r="M217" t="n">
-        <v>44272915</v>
-      </c>
-      <c r="N217" t="n">
-        <v>16923696</v>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>44272915</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>16923696</t>
+        </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -14395,11 +15237,15 @@
       <c r="L218" t="n">
         <v>90</v>
       </c>
-      <c r="M218" t="n">
-        <v>47055139</v>
-      </c>
-      <c r="N218" t="n">
-        <v>17369295</v>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>47055139</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>17369295</t>
+        </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -14459,11 +15305,15 @@
       <c r="L219" t="n">
         <v>99</v>
       </c>
-      <c r="M219" t="n">
-        <v>47470005</v>
-      </c>
-      <c r="N219" t="n">
-        <v>17367914</v>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>47470005</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>17367914</t>
+        </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -14523,11 +15373,15 @@
       <c r="L220" t="n">
         <v>104</v>
       </c>
-      <c r="M220" t="n">
-        <v>47062748</v>
-      </c>
-      <c r="N220" t="n">
-        <v>17468256</v>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>47062748</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>17468256</t>
+        </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
@@ -14587,11 +15441,15 @@
       <c r="L221" t="n">
         <v>42</v>
       </c>
-      <c r="M221" t="n">
-        <v>355065580</v>
-      </c>
-      <c r="N221" t="n">
-        <v>19368509</v>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>355065580</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>19368509</t>
+        </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -14655,8 +15513,10 @@
       <c r="L222" t="n">
         <v>18</v>
       </c>
-      <c r="M222" t="n">
-        <v>354931889</v>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>354931889</t>
+        </is>
       </c>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr">
@@ -14717,11 +15577,15 @@
       <c r="L223" t="n">
         <v>83</v>
       </c>
-      <c r="M223" t="n">
-        <v>50176387</v>
-      </c>
-      <c r="N223" t="n">
-        <v>18555232</v>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>50176387</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>18555232</t>
+        </is>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -14781,11 +15645,15 @@
       <c r="L224" t="n">
         <v>90</v>
       </c>
-      <c r="M224" t="n">
-        <v>51112083</v>
-      </c>
-      <c r="N224" t="n">
-        <v>20942923</v>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>51112083</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>20942923</t>
+        </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
@@ -14845,11 +15713,15 @@
       <c r="L225" t="n">
         <v>44</v>
       </c>
-      <c r="M225" t="n">
-        <v>358929637</v>
-      </c>
-      <c r="N225" t="n">
-        <v>20146658</v>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>358929637</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>20146658</t>
+        </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -14909,11 +15781,15 @@
       <c r="L226" t="n">
         <v>182</v>
       </c>
-      <c r="M226" t="n">
-        <v>50728652</v>
-      </c>
-      <c r="N226" t="n">
-        <v>20004377</v>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>50728652</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>20004377</t>
+        </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -14973,11 +15849,15 @@
       <c r="L227" t="n">
         <v>98</v>
       </c>
-      <c r="M227" t="n">
-        <v>358606680</v>
-      </c>
-      <c r="N227" t="n">
-        <v>20236107</v>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>358606680</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>20236107</t>
+        </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -15037,11 +15917,15 @@
       <c r="L228" t="n">
         <v>125</v>
       </c>
-      <c r="M228" t="n">
-        <v>51407172</v>
-      </c>
-      <c r="N228" t="n">
-        <v>21530058</v>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>51407172</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>21530058</t>
+        </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -15101,11 +15985,15 @@
       <c r="L229" t="n">
         <v>44</v>
       </c>
-      <c r="M229" t="n">
-        <v>362666414</v>
-      </c>
-      <c r="N229" t="n">
-        <v>21934452</v>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>362666414</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>21934452</t>
+        </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -15165,11 +16053,15 @@
       <c r="L230" t="n">
         <v>45</v>
       </c>
-      <c r="M230" t="n">
-        <v>361119442</v>
-      </c>
-      <c r="N230" t="n">
-        <v>20636232</v>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>361119442</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>20636232</t>
+        </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -15233,8 +16125,10 @@
       <c r="L231" t="n">
         <v>40</v>
       </c>
-      <c r="M231" t="n">
-        <v>51661279</v>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>51661279</t>
+        </is>
       </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr">
@@ -15295,11 +16189,15 @@
       <c r="L232" t="n">
         <v>73</v>
       </c>
-      <c r="M232" t="n">
-        <v>71975172</v>
-      </c>
-      <c r="N232" t="n">
-        <v>23267369</v>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>71975172</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>23267369</t>
+        </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
@@ -15359,11 +16257,15 @@
       <c r="L233" t="n">
         <v>82</v>
       </c>
-      <c r="M233" t="n">
-        <v>364846413</v>
-      </c>
-      <c r="N233" t="n">
-        <v>22338097</v>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>364846413</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>22338097</t>
+        </is>
       </c>
       <c r="O233" t="inlineStr">
         <is>
@@ -15423,11 +16325,15 @@
       <c r="L234" t="n">
         <v>87</v>
       </c>
-      <c r="M234" t="n">
-        <v>51960213</v>
-      </c>
-      <c r="N234" t="n">
-        <v>22503417</v>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>51960213</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>22503417</t>
+        </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
@@ -15487,11 +16393,15 @@
       <c r="L235" t="n">
         <v>102</v>
       </c>
-      <c r="M235" t="n">
-        <v>51822368</v>
-      </c>
-      <c r="N235" t="n">
-        <v>22261835</v>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>51822368</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>22261835</t>
+        </is>
       </c>
       <c r="O235" t="inlineStr">
         <is>
@@ -15551,11 +16461,15 @@
       <c r="L236" t="n">
         <v>109</v>
       </c>
-      <c r="M236" t="n">
-        <v>52329463</v>
-      </c>
-      <c r="N236" t="n">
-        <v>23200689</v>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>52329463</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>23200689</t>
+        </is>
       </c>
       <c r="O236" t="inlineStr">
         <is>
@@ -15615,11 +16529,15 @@
       <c r="L237" t="n">
         <v>73</v>
       </c>
-      <c r="M237" t="n">
-        <v>372347934</v>
-      </c>
-      <c r="N237" t="n">
-        <v>24371816</v>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>372347934</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>24371816</t>
+        </is>
       </c>
       <c r="O237" t="inlineStr">
         <is>
@@ -15679,11 +16597,15 @@
       <c r="L238" t="n">
         <v>103</v>
       </c>
-      <c r="M238" t="n">
-        <v>600205852</v>
-      </c>
-      <c r="N238" t="n">
-        <v>25150960</v>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>600205852</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>25150960</t>
+        </is>
       </c>
       <c r="O238" t="inlineStr">
         <is>
@@ -15747,8 +16669,10 @@
       <c r="L239" t="n">
         <v>55</v>
       </c>
-      <c r="M239" t="n">
-        <v>53069927</v>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>53069927</t>
+        </is>
       </c>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr">
@@ -15809,11 +16733,15 @@
       <c r="L240" t="n">
         <v>48</v>
       </c>
-      <c r="M240" t="n">
-        <v>370454068</v>
-      </c>
-      <c r="N240" t="n">
-        <v>24971127</v>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>370454068</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>24971127</t>
+        </is>
       </c>
       <c r="O240" t="inlineStr">
         <is>
@@ -15873,11 +16801,15 @@
       <c r="L241" t="n">
         <v>60</v>
       </c>
-      <c r="M241" t="n">
-        <v>601522362</v>
-      </c>
-      <c r="N241" t="n">
-        <v>25664123</v>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>601522362</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>25664123</t>
+        </is>
       </c>
       <c r="O241" t="inlineStr">
         <is>
@@ -15937,11 +16869,15 @@
       <c r="L242" t="n">
         <v>53</v>
       </c>
-      <c r="M242" t="n">
-        <v>610812873</v>
-      </c>
-      <c r="N242" t="n">
-        <v>25222360</v>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>610812873</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>25222360</t>
+        </is>
       </c>
       <c r="O242" t="inlineStr">
         <is>
@@ -16001,11 +16937,15 @@
       <c r="L243" t="n">
         <v>90</v>
       </c>
-      <c r="M243" t="n">
-        <v>52917089</v>
-      </c>
-      <c r="N243" t="n">
-        <v>24337962</v>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>52917089</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>24337962</t>
+        </is>
       </c>
       <c r="O243" t="inlineStr">
         <is>
@@ -16065,11 +17005,15 @@
       <c r="L244" t="n">
         <v>45</v>
       </c>
-      <c r="M244" t="n">
-        <v>53069672</v>
-      </c>
-      <c r="N244" t="n">
-        <v>24680396</v>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>53069672</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>24680396</t>
+        </is>
       </c>
       <c r="O244" t="inlineStr">
         <is>
@@ -16129,11 +17073,15 @@
       <c r="L245" t="n">
         <v>152</v>
       </c>
-      <c r="M245" t="n">
-        <v>52962187</v>
-      </c>
-      <c r="N245" t="n">
-        <v>24418062</v>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>52962187</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>24418062</t>
+        </is>
       </c>
       <c r="O245" t="inlineStr">
         <is>
@@ -16193,11 +17141,15 @@
       <c r="L246" t="n">
         <v>114</v>
       </c>
-      <c r="M246" t="n">
-        <v>373517812</v>
-      </c>
-      <c r="N246" t="n">
-        <v>24945113</v>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>373517812</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>24945113</t>
+        </is>
       </c>
       <c r="O246" t="inlineStr">
         <is>
@@ -16257,11 +17209,15 @@
       <c r="L247" t="n">
         <v>106</v>
       </c>
-      <c r="M247" t="n">
-        <v>373746360</v>
-      </c>
-      <c r="N247" t="n">
-        <v>24873996</v>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>373746360</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>24873996</t>
+        </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
@@ -16321,11 +17277,15 @@
       <c r="L248" t="n">
         <v>93</v>
       </c>
-      <c r="M248" t="n">
-        <v>52965149</v>
-      </c>
-      <c r="N248" t="n">
-        <v>24410809</v>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>52965149</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>24410809</t>
+        </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
@@ -16385,11 +17345,15 @@
       <c r="L249" t="n">
         <v>115</v>
       </c>
-      <c r="M249" t="n">
-        <v>606318820</v>
-      </c>
-      <c r="N249" t="n">
-        <v>26223675</v>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>606318820</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>26223675</t>
+        </is>
       </c>
       <c r="O249" t="inlineStr">
         <is>
@@ -16449,11 +17413,15 @@
       <c r="L250" t="n">
         <v>109</v>
       </c>
-      <c r="M250" t="n">
-        <v>608514878</v>
-      </c>
-      <c r="N250" t="n">
-        <v>26498178</v>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>608514878</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>26498178</t>
+        </is>
       </c>
       <c r="O250" t="inlineStr">
         <is>
@@ -16513,11 +17481,15 @@
       <c r="L251" t="n">
         <v>82</v>
       </c>
-      <c r="M251" t="n">
-        <v>601107743</v>
-      </c>
-      <c r="N251" t="n">
-        <v>25417943</v>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>601107743</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>25417943</t>
+        </is>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -16577,11 +17549,15 @@
       <c r="L252" t="n">
         <v>75</v>
       </c>
-      <c r="M252" t="n">
-        <v>607156696</v>
-      </c>
-      <c r="N252" t="n">
-        <v>26370557</v>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>607156696</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>26370557</t>
+        </is>
       </c>
       <c r="O252" t="inlineStr">
         <is>
@@ -16641,11 +17617,15 @@
       <c r="L253" t="n">
         <v>42</v>
       </c>
-      <c r="M253" t="n">
-        <v>602903781</v>
-      </c>
-      <c r="N253" t="n">
-        <v>24803007</v>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>602903781</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>24803007</t>
+        </is>
       </c>
       <c r="O253" t="inlineStr">
         <is>
@@ -16705,11 +17685,15 @@
       <c r="L254" t="n">
         <v>47</v>
       </c>
-      <c r="M254" t="n">
-        <v>606507291</v>
-      </c>
-      <c r="N254" t="n">
-        <v>26479686</v>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>606507291</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>26479686</t>
+        </is>
       </c>
       <c r="O254" t="inlineStr">
         <is>
@@ -16769,11 +17753,15 @@
       <c r="L255" t="n">
         <v>118</v>
       </c>
-      <c r="M255" t="n">
-        <v>607639977</v>
-      </c>
-      <c r="N255" t="n">
-        <v>26654973</v>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>607639977</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>26654973</t>
+        </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
@@ -16838,8 +17826,10 @@
         <v>53</v>
       </c>
       <c r="M256" t="inlineStr"/>
-      <c r="N256" t="n">
-        <v>27686055</v>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>27686055</t>
+        </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
@@ -16899,11 +17889,15 @@
       <c r="L257" t="n">
         <v>77</v>
       </c>
-      <c r="M257" t="n">
-        <v>610218440</v>
-      </c>
-      <c r="N257" t="n">
-        <v>27157933</v>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>610218440</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>27157933</t>
+        </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
@@ -16963,11 +17957,15 @@
       <c r="L258" t="n">
         <v>62</v>
       </c>
-      <c r="M258" t="n">
-        <v>609389369</v>
-      </c>
-      <c r="N258" t="n">
-        <v>27066074</v>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>609389369</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>27066074</t>
+        </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
@@ -17027,11 +18025,15 @@
       <c r="L259" t="n">
         <v>54</v>
       </c>
-      <c r="M259" t="n">
-        <v>616994993</v>
-      </c>
-      <c r="N259" t="n">
-        <v>28449632</v>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>616994993</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>28449632</t>
+        </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -17091,11 +18093,15 @@
       <c r="L260" t="n">
         <v>111</v>
       </c>
-      <c r="M260" t="n">
-        <v>617700580</v>
-      </c>
-      <c r="N260" t="n">
-        <v>28778282</v>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>617700580</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>28778282</t>
+        </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
@@ -17155,11 +18161,15 @@
       <c r="L261" t="n">
         <v>32</v>
       </c>
-      <c r="M261" t="n">
-        <v>619110037</v>
-      </c>
-      <c r="N261" t="n">
-        <v>28981984</v>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>619110037</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>28981984</t>
+        </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
@@ -17219,11 +18229,15 @@
       <c r="L262" t="n">
         <v>85</v>
       </c>
-      <c r="M262" t="n">
-        <v>617760490</v>
-      </c>
-      <c r="N262" t="n">
-        <v>28802704</v>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>617760490</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>28802704</t>
+        </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
@@ -17283,11 +18297,15 @@
       <c r="L263" t="n">
         <v>149</v>
       </c>
-      <c r="M263" t="n">
-        <v>43466615</v>
-      </c>
-      <c r="N263" t="n">
-        <v>16604826</v>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>43466615</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>16604826</t>
+        </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
@@ -17347,11 +18365,15 @@
       <c r="L264" t="n">
         <v>121</v>
       </c>
-      <c r="M264" t="n">
-        <v>618009055</v>
-      </c>
-      <c r="N264" t="n">
-        <v>28854590</v>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>618009055</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>28854590</t>
+        </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
@@ -17411,11 +18433,15 @@
       <c r="L265" t="n">
         <v>136</v>
       </c>
-      <c r="M265" t="n">
-        <v>44602052</v>
-      </c>
-      <c r="N265" t="n">
-        <v>17070196</v>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>44602052</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>17070196</t>
+        </is>
       </c>
       <c r="O265" t="inlineStr">
         <is>
@@ -17475,11 +18501,15 @@
       <c r="L266" t="n">
         <v>143</v>
       </c>
-      <c r="M266" t="n">
-        <v>50029366</v>
-      </c>
-      <c r="N266" t="n">
-        <v>18177867</v>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>50029366</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>18177867</t>
+        </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
@@ -17539,11 +18569,15 @@
       <c r="L267" t="n">
         <v>105</v>
       </c>
-      <c r="M267" t="n">
-        <v>50382594</v>
-      </c>
-      <c r="N267" t="n">
-        <v>19127427</v>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>50382594</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>19127427</t>
+        </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
@@ -17603,11 +18637,15 @@
       <c r="L268" t="n">
         <v>537</v>
       </c>
-      <c r="M268" t="n">
-        <v>373471770</v>
-      </c>
-      <c r="N268" t="n">
-        <v>25006718</v>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>373471770</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>25006718</t>
+        </is>
       </c>
       <c r="O268" t="inlineStr">
         <is>
@@ -17667,11 +18705,15 @@
       <c r="L269" t="n">
         <v>64</v>
       </c>
-      <c r="M269" t="n">
-        <v>616521197</v>
-      </c>
-      <c r="N269" t="n">
-        <v>28557652</v>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>616521197</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>28557652</t>
+        </is>
       </c>
       <c r="O269" t="inlineStr">
         <is>
@@ -17731,11 +18773,15 @@
       <c r="L270" t="n">
         <v>63</v>
       </c>
-      <c r="M270" t="n">
-        <v>51657796</v>
-      </c>
-      <c r="N270" t="n">
-        <v>21984038</v>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>51657796</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>21984038</t>
+        </is>
       </c>
       <c r="O270" t="inlineStr">
         <is>
@@ -17795,11 +18841,15 @@
       <c r="L271" t="n">
         <v>63</v>
       </c>
-      <c r="M271" t="n">
-        <v>51657796</v>
-      </c>
-      <c r="N271" t="n">
-        <v>21984038</v>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>51657796</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>21984038</t>
+        </is>
       </c>
       <c r="O271" t="inlineStr">
         <is>
@@ -17859,11 +18909,15 @@
       <c r="L272" t="n">
         <v>119</v>
       </c>
-      <c r="M272" t="n">
-        <v>365218029</v>
-      </c>
-      <c r="N272" t="n">
-        <v>22870010</v>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>365218029</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>22870010</t>
+        </is>
       </c>
       <c r="O272" t="inlineStr">
         <is>
@@ -17923,11 +18977,15 @@
       <c r="L273" t="n">
         <v>108</v>
       </c>
-      <c r="M273" t="n">
-        <v>44445018</v>
-      </c>
-      <c r="N273" t="n">
-        <v>16478764</v>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>44445018</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>16478764</t>
+        </is>
       </c>
       <c r="O273" t="inlineStr">
         <is>
@@ -17987,11 +19045,15 @@
       <c r="L274" t="n">
         <v>39</v>
       </c>
-      <c r="M274" t="n">
-        <v>358989835</v>
-      </c>
-      <c r="N274" t="n">
-        <v>20337206</v>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>358989835</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>20337206</t>
+        </is>
       </c>
       <c r="O274" t="inlineStr">
         <is>
@@ -18051,11 +19113,15 @@
       <c r="L275" t="n">
         <v>113</v>
       </c>
-      <c r="M275" t="n">
-        <v>352855029</v>
-      </c>
-      <c r="N275" t="n">
-        <v>18794162</v>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>352855029</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>18794162</t>
+        </is>
       </c>
       <c r="O275" t="inlineStr">
         <is>
@@ -18115,11 +19181,15 @@
       <c r="L276" t="n">
         <v>121</v>
       </c>
-      <c r="M276" t="n">
-        <v>618009055</v>
-      </c>
-      <c r="N276" t="n">
-        <v>28854590</v>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>618009055</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>28854590</t>
+        </is>
       </c>
       <c r="O276" t="inlineStr">
         <is>
@@ -18179,11 +19249,15 @@
       <c r="L277" t="n">
         <v>149</v>
       </c>
-      <c r="M277" t="n">
-        <v>43466615</v>
-      </c>
-      <c r="N277" t="n">
-        <v>16604826</v>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>43466615</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>16604826</t>
+        </is>
       </c>
       <c r="O277" t="inlineStr">
         <is>
@@ -18243,11 +19317,15 @@
       <c r="L278" t="n">
         <v>136</v>
       </c>
-      <c r="M278" t="n">
-        <v>44602052</v>
-      </c>
-      <c r="N278" t="n">
-        <v>17070196</v>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>44602052</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>17070196</t>
+        </is>
       </c>
       <c r="O278" t="inlineStr">
         <is>
@@ -18307,11 +19385,15 @@
       <c r="L279" t="n">
         <v>143</v>
       </c>
-      <c r="M279" t="n">
-        <v>50029366</v>
-      </c>
-      <c r="N279" t="n">
-        <v>18177867</v>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>50029366</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>18177867</t>
+        </is>
       </c>
       <c r="O279" t="inlineStr">
         <is>
@@ -18371,11 +19453,15 @@
       <c r="L280" t="n">
         <v>55</v>
       </c>
-      <c r="M280" t="n">
-        <v>369338943</v>
-      </c>
-      <c r="N280" t="n">
-        <v>23379651</v>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>369338943</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>23379651</t>
+        </is>
       </c>
       <c r="O280" t="inlineStr">
         <is>
@@ -18435,11 +19521,15 @@
       <c r="L281" t="n">
         <v>290</v>
       </c>
-      <c r="M281" t="n">
-        <v>29364624</v>
-      </c>
-      <c r="N281" t="n">
-        <v>10438996</v>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>29364624</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>10438996</t>
+        </is>
       </c>
       <c r="O281" t="inlineStr">
         <is>
@@ -18499,11 +19589,15 @@
       <c r="L282" t="n">
         <v>367</v>
       </c>
-      <c r="M282" t="n">
-        <v>34158220</v>
-      </c>
-      <c r="N282" t="n">
-        <v>11836287</v>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>34158220</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>11836287</t>
+        </is>
       </c>
       <c r="O282" t="inlineStr">
         <is>
@@ -18563,11 +19657,15 @@
       <c r="L283" t="n">
         <v>105</v>
       </c>
-      <c r="M283" t="n">
-        <v>50382594</v>
-      </c>
-      <c r="N283" t="n">
-        <v>19127427</v>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>50382594</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>19127427</t>
+        </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
@@ -18627,11 +19725,15 @@
       <c r="L284" t="n">
         <v>51</v>
       </c>
-      <c r="M284" t="n">
-        <v>52765836</v>
-      </c>
-      <c r="N284" t="n">
-        <v>24014214</v>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>52765836</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>24014214</t>
+        </is>
       </c>
       <c r="O284" t="inlineStr">
         <is>
@@ -18691,11 +19793,15 @@
       <c r="L285" t="n">
         <v>129</v>
       </c>
-      <c r="M285" t="n">
-        <v>36236262</v>
-      </c>
-      <c r="N285" t="n">
-        <v>12571165</v>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>36236262</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>12571165</t>
+        </is>
       </c>
       <c r="O285" t="inlineStr">
         <is>
@@ -18755,11 +19861,15 @@
       <c r="L286" t="n">
         <v>313</v>
       </c>
-      <c r="M286" t="n">
-        <v>39092044</v>
-      </c>
-      <c r="N286" t="n">
-        <v>15302293</v>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>39092044</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>15302293</t>
+        </is>
       </c>
       <c r="O286" t="inlineStr">
         <is>
@@ -18819,11 +19929,15 @@
       <c r="L287" t="n">
         <v>105</v>
       </c>
-      <c r="M287" t="n">
-        <v>364097670</v>
-      </c>
-      <c r="N287" t="n">
-        <v>22128296</v>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>364097670</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>22128296</t>
+        </is>
       </c>
       <c r="O287" t="inlineStr">
         <is>
@@ -18883,11 +19997,15 @@
       <c r="L288" t="n">
         <v>106</v>
       </c>
-      <c r="M288" t="n">
-        <v>359396415</v>
-      </c>
-      <c r="N288" t="n">
-        <v>20435692</v>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>359396415</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>20435692</t>
+        </is>
       </c>
       <c r="O288" t="inlineStr">
         <is>
@@ -18947,11 +20065,15 @@
       <c r="L289" t="n">
         <v>61</v>
       </c>
-      <c r="M289" t="n">
-        <v>607202007</v>
-      </c>
-      <c r="N289" t="n">
-        <v>26752854</v>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>607202007</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>26752854</t>
+        </is>
       </c>
       <c r="O289" t="inlineStr">
         <is>
@@ -19011,11 +20133,15 @@
       <c r="L290" t="n">
         <v>301</v>
       </c>
-      <c r="M290" t="n">
-        <v>34093900</v>
-      </c>
-      <c r="N290" t="n">
-        <v>11779598</v>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>34093900</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>11779598</t>
+        </is>
       </c>
       <c r="O290" t="inlineStr">
         <is>
@@ -19075,11 +20201,15 @@
       <c r="L291" t="n">
         <v>108</v>
       </c>
-      <c r="M291" t="n">
-        <v>362168413</v>
-      </c>
-      <c r="N291" t="n">
-        <v>21606131</v>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>362168413</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>21606131</t>
+        </is>
       </c>
       <c r="O291" t="inlineStr">
         <is>
@@ -19139,11 +20269,15 @@
       <c r="L292" t="n">
         <v>64</v>
       </c>
-      <c r="M292" t="n">
-        <v>616521197</v>
-      </c>
-      <c r="N292" t="n">
-        <v>28557652</v>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>616521197</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>28557652</t>
+        </is>
       </c>
       <c r="O292" t="inlineStr">
         <is>
@@ -19203,11 +20337,15 @@
       <c r="L293" t="n">
         <v>92</v>
       </c>
-      <c r="M293" t="n">
-        <v>39335259</v>
-      </c>
-      <c r="N293" t="n">
-        <v>15511336</v>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>39335259</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>15511336</t>
+        </is>
       </c>
       <c r="O293" t="inlineStr">
         <is>
@@ -19267,11 +20405,15 @@
       <c r="L294" t="n">
         <v>1015</v>
       </c>
-      <c r="M294" t="n">
-        <v>46220816</v>
-      </c>
-      <c r="N294" t="n">
-        <v>17287476</v>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>46220816</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>17287476</t>
+        </is>
       </c>
       <c r="O294" t="inlineStr">
         <is>
@@ -19331,11 +20473,15 @@
       <c r="L295" t="n">
         <v>537</v>
       </c>
-      <c r="M295" t="n">
-        <v>373471770</v>
-      </c>
-      <c r="N295" t="n">
-        <v>25006718</v>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>373471770</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>25006718</t>
+        </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
@@ -19395,11 +20541,15 @@
       <c r="L296" t="n">
         <v>252</v>
       </c>
-      <c r="M296" t="n">
-        <v>364771372</v>
-      </c>
-      <c r="N296" t="n">
-        <v>22419702</v>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>364771372</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>22419702</t>
+        </is>
       </c>
       <c r="O296" t="inlineStr">
         <is>
@@ -19459,11 +20609,15 @@
       <c r="L297" t="n">
         <v>63</v>
       </c>
-      <c r="M297" t="n">
-        <v>51657796</v>
-      </c>
-      <c r="N297" t="n">
-        <v>21984038</v>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>51657796</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>21984038</t>
+        </is>
       </c>
       <c r="O297" t="inlineStr">
         <is>
@@ -19523,11 +20677,15 @@
       <c r="L298" t="n">
         <v>213</v>
       </c>
-      <c r="M298" t="n">
-        <v>32768540</v>
-      </c>
-      <c r="N298" t="n">
-        <v>11473953</v>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>32768540</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>11473953</t>
+        </is>
       </c>
       <c r="O298" t="inlineStr">
         <is>
@@ -19587,11 +20745,15 @@
       <c r="L299" t="n">
         <v>52</v>
       </c>
-      <c r="M299" t="n">
-        <v>355551364</v>
-      </c>
-      <c r="N299" t="n">
-        <v>19757275</v>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>355551364</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>19757275</t>
+        </is>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -19651,11 +20813,15 @@
       <c r="L300" t="n">
         <v>119</v>
       </c>
-      <c r="M300" t="n">
-        <v>365218029</v>
-      </c>
-      <c r="N300" t="n">
-        <v>22870010</v>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>365218029</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>22870010</t>
+        </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
@@ -19715,11 +20881,15 @@
       <c r="L301" t="n">
         <v>103</v>
       </c>
-      <c r="M301" t="n">
-        <v>38456778</v>
-      </c>
-      <c r="N301" t="n">
-        <v>15063963</v>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>38456778</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>15063963</t>
+        </is>
       </c>
       <c r="O301" t="inlineStr">
         <is>
@@ -19779,11 +20949,15 @@
       <c r="L302" t="n">
         <v>42</v>
       </c>
-      <c r="M302" t="n">
-        <v>50499867</v>
-      </c>
-      <c r="N302" t="n">
-        <v>19396538</v>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>50499867</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>19396538</t>
+        </is>
       </c>
       <c r="O302" t="inlineStr">
         <is>
@@ -19843,11 +21017,15 @@
       <c r="L303" t="n">
         <v>108</v>
       </c>
-      <c r="M303" t="n">
-        <v>44445018</v>
-      </c>
-      <c r="N303" t="n">
-        <v>16478764</v>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>44445018</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>16478764</t>
+        </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
@@ -19911,11 +21089,15 @@
       <c r="L304" t="n">
         <v>388</v>
       </c>
-      <c r="M304" t="n">
-        <v>41794294</v>
-      </c>
-      <c r="N304" t="n">
-        <v>16199429</v>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>41794294</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>16199429</t>
+        </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
@@ -19975,11 +21157,15 @@
       <c r="L305" t="n">
         <v>393</v>
       </c>
-      <c r="M305" t="n">
-        <v>32112107</v>
-      </c>
-      <c r="N305" t="n">
-        <v>11172832</v>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>32112107</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>11172832</t>
+        </is>
       </c>
       <c r="O305" t="inlineStr">
         <is>
@@ -20039,11 +21225,15 @@
       <c r="L306" t="n">
         <v>39</v>
       </c>
-      <c r="M306" t="n">
-        <v>358989835</v>
-      </c>
-      <c r="N306" t="n">
-        <v>20337206</v>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>358989835</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>20337206</t>
+        </is>
       </c>
       <c r="O306" t="inlineStr">
         <is>
@@ -20103,11 +21293,15 @@
       <c r="L307" t="n">
         <v>214</v>
       </c>
-      <c r="M307" t="n">
-        <v>38147069</v>
-      </c>
-      <c r="N307" t="n">
-        <v>14739186</v>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>38147069</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>14739186</t>
+        </is>
       </c>
       <c r="O307" t="inlineStr">
         <is>
@@ -20167,11 +21361,15 @@
       <c r="L308" t="n">
         <v>55</v>
       </c>
-      <c r="M308" t="n">
-        <v>369338943</v>
-      </c>
-      <c r="N308" t="n">
-        <v>23379651</v>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>369338943</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>23379651</t>
+        </is>
       </c>
       <c r="O308" t="inlineStr">
         <is>
@@ -20231,11 +21429,15 @@
       <c r="L309" t="n">
         <v>290</v>
       </c>
-      <c r="M309" t="n">
-        <v>29364624</v>
-      </c>
-      <c r="N309" t="n">
-        <v>10438996</v>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>29364624</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>10438996</t>
+        </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
@@ -20295,11 +21497,15 @@
       <c r="L310" t="n">
         <v>148</v>
       </c>
-      <c r="M310" t="n">
-        <v>34831744</v>
-      </c>
-      <c r="N310" t="n">
-        <v>12137881</v>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>34831744</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>12137881</t>
+        </is>
       </c>
       <c r="O310" t="inlineStr">
         <is>
@@ -20359,11 +21565,15 @@
       <c r="L311" t="n">
         <v>105</v>
       </c>
-      <c r="M311" t="n">
-        <v>50382594</v>
-      </c>
-      <c r="N311" t="n">
-        <v>19127427</v>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>50382594</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>19127427</t>
+        </is>
       </c>
       <c r="O311" t="inlineStr">
         <is>
@@ -20423,11 +21633,15 @@
       <c r="L312" t="n">
         <v>51</v>
       </c>
-      <c r="M312" t="n">
-        <v>52765836</v>
-      </c>
-      <c r="N312" t="n">
-        <v>24014214</v>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>52765836</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>24014214</t>
+        </is>
       </c>
       <c r="O312" t="inlineStr">
         <is>
@@ -20487,11 +21701,15 @@
       <c r="L313" t="n">
         <v>129</v>
       </c>
-      <c r="M313" t="n">
-        <v>36236262</v>
-      </c>
-      <c r="N313" t="n">
-        <v>12571165</v>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>36236262</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>12571165</t>
+        </is>
       </c>
       <c r="O313" t="inlineStr">
         <is>
@@ -20551,11 +21769,15 @@
       <c r="L314" t="n">
         <v>105</v>
       </c>
-      <c r="M314" t="n">
-        <v>364097670</v>
-      </c>
-      <c r="N314" t="n">
-        <v>22128296</v>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>364097670</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>22128296</t>
+        </is>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -20615,11 +21837,15 @@
       <c r="L315" t="n">
         <v>92</v>
       </c>
-      <c r="M315" t="n">
-        <v>39335259</v>
-      </c>
-      <c r="N315" t="n">
-        <v>15511336</v>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>39335259</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>15511336</t>
+        </is>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -20679,11 +21905,15 @@
       <c r="L316" t="n">
         <v>53</v>
       </c>
-      <c r="M316" t="n">
-        <v>38146002</v>
-      </c>
-      <c r="N316" t="n">
-        <v>12764624</v>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>38146002</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>12764624</t>
+        </is>
       </c>
       <c r="O316" t="inlineStr">
         <is>
@@ -20747,8 +21977,10 @@
       <c r="L317" t="n">
         <v>16</v>
       </c>
-      <c r="M317" t="n">
-        <v>623600800</v>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>623600800</t>
+        </is>
       </c>
       <c r="N317" t="inlineStr"/>
       <c r="O317" t="inlineStr">
@@ -20809,11 +22041,15 @@
       <c r="L318" t="n">
         <v>203</v>
       </c>
-      <c r="M318" t="n">
-        <v>34168428</v>
-      </c>
-      <c r="N318" t="n">
-        <v>11821265</v>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>34168428</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>11821265</t>
+        </is>
       </c>
       <c r="O318" t="inlineStr">
         <is>
@@ -20873,11 +22109,15 @@
       <c r="L319" t="n">
         <v>113</v>
       </c>
-      <c r="M319" t="n">
-        <v>352855029</v>
-      </c>
-      <c r="N319" t="n">
-        <v>18794162</v>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>352855029</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>18794162</t>
+        </is>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -20937,11 +22177,15 @@
       <c r="L320" t="n">
         <v>214</v>
       </c>
-      <c r="M320" t="n">
-        <v>38147069</v>
-      </c>
-      <c r="N320" t="n">
-        <v>14739186</v>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>38147069</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>14739186</t>
+        </is>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -21001,11 +22245,15 @@
       <c r="L321" t="n">
         <v>148</v>
       </c>
-      <c r="M321" t="n">
-        <v>34831744</v>
-      </c>
-      <c r="N321" t="n">
-        <v>12137881</v>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>34831744</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>12137881</t>
+        </is>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -21065,11 +22313,15 @@
       <c r="L322" t="n">
         <v>83</v>
       </c>
-      <c r="M322" t="n">
-        <v>50424371</v>
-      </c>
-      <c r="N322" t="n">
-        <v>19214545</v>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>50424371</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>19214545</t>
+        </is>
       </c>
       <c r="O322" t="inlineStr">
         <is>
@@ -21133,8 +22385,10 @@
       <c r="L323" t="n">
         <v>34</v>
       </c>
-      <c r="M323" t="n">
-        <v>46092405</v>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>46092405</t>
+        </is>
       </c>
       <c r="N323" t="inlineStr"/>
       <c r="O323" t="inlineStr">
@@ -21199,8 +22453,10 @@
       <c r="L324" t="n">
         <v>16</v>
       </c>
-      <c r="M324" t="n">
-        <v>623600800</v>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>623600800</t>
+        </is>
       </c>
       <c r="N324" t="inlineStr"/>
       <c r="O324" t="inlineStr">
@@ -21325,11 +22581,15 @@
       <c r="L326" t="n">
         <v>61</v>
       </c>
-      <c r="M326" t="n">
-        <v>40204875</v>
-      </c>
-      <c r="N326" t="n">
-        <v>15755044</v>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>40204875</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>15755044</t>
+        </is>
       </c>
       <c r="O326" t="inlineStr">
         <is>
@@ -21389,11 +22649,15 @@
       <c r="L327" t="n">
         <v>451</v>
       </c>
-      <c r="M327" t="n">
-        <v>351074945</v>
-      </c>
-      <c r="N327" t="n">
-        <v>17462639</v>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>351074945</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>17462639</t>
+        </is>
       </c>
       <c r="O327" t="inlineStr">
         <is>
@@ -21453,11 +22717,15 @@
       <c r="L328" t="n">
         <v>40</v>
       </c>
-      <c r="M328" t="n">
-        <v>52000521</v>
-      </c>
-      <c r="N328" t="n">
-        <v>22569710</v>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>52000521</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>22569710</t>
+        </is>
       </c>
       <c r="O328" t="inlineStr">
         <is>
@@ -21522,8 +22790,10 @@
         <v>113</v>
       </c>
       <c r="M329" t="inlineStr"/>
-      <c r="N329" t="n">
-        <v>18802744</v>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>18802744</t>
+        </is>
       </c>
       <c r="O329" t="inlineStr">
         <is>
@@ -21583,11 +22853,15 @@
       <c r="L330" t="n">
         <v>63</v>
       </c>
-      <c r="M330" t="n">
-        <v>47055140</v>
-      </c>
-      <c r="N330" t="n">
-        <v>17347165</v>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>47055140</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>17347165</t>
+        </is>
       </c>
       <c r="O330" t="inlineStr">
         <is>
@@ -21647,11 +22921,15 @@
       <c r="L331" t="n">
         <v>168</v>
       </c>
-      <c r="M331" t="n">
-        <v>358307115</v>
-      </c>
-      <c r="N331" t="n">
-        <v>20008886</v>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>358307115</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>20008886</t>
+        </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
@@ -21711,11 +22989,15 @@
       <c r="L332" t="n">
         <v>69</v>
       </c>
-      <c r="M332" t="n">
-        <v>43941413</v>
-      </c>
-      <c r="N332" t="n">
-        <v>16785142</v>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>43941413</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>16785142</t>
+        </is>
       </c>
       <c r="O332" t="inlineStr">
         <is>
@@ -21775,11 +23057,15 @@
       <c r="L333" t="n">
         <v>81</v>
       </c>
-      <c r="M333" t="n">
-        <v>36760721</v>
-      </c>
-      <c r="N333" t="n">
-        <v>12857428</v>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>36760721</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>12857428</t>
+        </is>
       </c>
       <c r="O333" t="inlineStr">
         <is>
@@ -21839,11 +23125,15 @@
       <c r="L334" t="n">
         <v>88</v>
       </c>
-      <c r="M334" t="n">
-        <v>614689803</v>
-      </c>
-      <c r="N334" t="n">
-        <v>27816925</v>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>614689803</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>27816925</t>
+        </is>
       </c>
       <c r="O334" t="inlineStr">
         <is>
@@ -21903,11 +23193,15 @@
       <c r="L335" t="n">
         <v>67</v>
       </c>
-      <c r="M335" t="n">
-        <v>41317755</v>
-      </c>
-      <c r="N335" t="n">
-        <v>16169430</v>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>41317755</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>16169430</t>
+        </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
@@ -21967,11 +23261,15 @@
       <c r="L336" t="n">
         <v>138</v>
       </c>
-      <c r="M336" t="n">
-        <v>38807702</v>
-      </c>
-      <c r="N336" t="n">
-        <v>15117902</v>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>38807702</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>15117902</t>
+        </is>
       </c>
       <c r="O336" t="inlineStr">
         <is>
@@ -22031,11 +23329,15 @@
       <c r="L337" t="n">
         <v>108</v>
       </c>
-      <c r="M337" t="n">
-        <v>362168413</v>
-      </c>
-      <c r="N337" t="n">
-        <v>21606131</v>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>362168413</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>21606131</t>
+        </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
@@ -22095,11 +23397,15 @@
       <c r="L338" t="n">
         <v>52</v>
       </c>
-      <c r="M338" t="n">
-        <v>355551364</v>
-      </c>
-      <c r="N338" t="n">
-        <v>19757275</v>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>355551364</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>19757275</t>
+        </is>
       </c>
       <c r="O338" t="inlineStr">
         <is>
@@ -22159,11 +23465,15 @@
       <c r="L339" t="n">
         <v>290</v>
       </c>
-      <c r="M339" t="n">
-        <v>44445016</v>
-      </c>
-      <c r="N339" t="n">
-        <v>16501038</v>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>44445016</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>16501038</t>
+        </is>
       </c>
       <c r="O339" t="inlineStr">
         <is>
@@ -22225,8 +23535,10 @@
       <c r="L340" t="n">
         <v>23</v>
       </c>
-      <c r="M340" t="n">
-        <v>2008498423</v>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>2008498423</t>
+        </is>
       </c>
       <c r="N340" t="inlineStr"/>
       <c r="O340" t="inlineStr">
@@ -22285,11 +23597,15 @@
       <c r="L341" t="n">
         <v>35</v>
       </c>
-      <c r="M341" t="n">
-        <v>44407877</v>
-      </c>
-      <c r="N341" t="n">
-        <v>17009635</v>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>44407877</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>17009635</t>
+        </is>
       </c>
       <c r="O341" t="inlineStr">
         <is>
@@ -22347,11 +23663,15 @@
       <c r="L342" t="n">
         <v>35</v>
       </c>
-      <c r="M342" t="n">
-        <v>2016973002</v>
-      </c>
-      <c r="N342" t="n">
-        <v>35151930</v>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>2016973002</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>35151930</t>
+        </is>
       </c>
       <c r="O342" t="inlineStr">
         <is>
@@ -22409,11 +23729,15 @@
       <c r="L343" t="n">
         <v>118</v>
       </c>
-      <c r="M343" t="n">
-        <v>350060648</v>
-      </c>
-      <c r="N343" t="n">
-        <v>17898989</v>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>350060648</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>17898989</t>
+        </is>
       </c>
       <c r="O343" t="inlineStr">
         <is>
@@ -22471,11 +23795,15 @@
       <c r="L344" t="n">
         <v>87</v>
       </c>
-      <c r="M344" t="n">
-        <v>624012325</v>
-      </c>
-      <c r="N344" t="n">
-        <v>29320957</v>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>624012325</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>29320957</t>
+        </is>
       </c>
       <c r="O344" t="inlineStr">
         <is>
@@ -22533,11 +23861,15 @@
       <c r="L345" t="n">
         <v>197</v>
       </c>
-      <c r="M345" t="n">
-        <v>34521499</v>
-      </c>
-      <c r="N345" t="n">
-        <v>11994353</v>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>34521499</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>11994353</t>
+        </is>
       </c>
       <c r="O345" t="inlineStr">
         <is>
@@ -22597,11 +23929,15 @@
       <c r="L346" t="n">
         <v>40</v>
       </c>
-      <c r="M346" t="n">
-        <v>373318793</v>
-      </c>
-      <c r="N346" t="n">
-        <v>24992782</v>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>373318793</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>24992782</t>
+        </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
@@ -22661,11 +23997,15 @@
       <c r="L347" t="n">
         <v>49</v>
       </c>
-      <c r="M347" t="n">
-        <v>628944072</v>
-      </c>
-      <c r="N347" t="n">
-        <v>29483674</v>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>628944072</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>29483674</t>
+        </is>
       </c>
       <c r="O347" t="inlineStr">
         <is>
@@ -22725,11 +24065,15 @@
       <c r="L348" t="n">
         <v>49</v>
       </c>
-      <c r="M348" t="n">
-        <v>603252738</v>
-      </c>
-      <c r="N348" t="n">
-        <v>24447981</v>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>603252738</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>24447981</t>
+        </is>
       </c>
       <c r="O348" t="inlineStr">
         <is>
@@ -22787,11 +24131,15 @@
       <c r="L349" t="n">
         <v>25</v>
       </c>
-      <c r="M349" t="n">
-        <v>604326040</v>
-      </c>
-      <c r="N349" t="n">
-        <v>25807833</v>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>604326040</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>25807833</t>
+        </is>
       </c>
       <c r="O349" t="inlineStr">
         <is>
@@ -22849,11 +24197,15 @@
       <c r="L350" t="n">
         <v>59</v>
       </c>
-      <c r="M350" t="n">
-        <v>2014888355</v>
-      </c>
-      <c r="N350" t="n">
-        <v>34610894</v>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>2014888355</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>34610894</t>
+        </is>
       </c>
       <c r="O350" t="inlineStr">
         <is>
@@ -22911,11 +24263,15 @@
       <c r="L351" t="n">
         <v>421</v>
       </c>
-      <c r="M351" t="n">
-        <v>43020236</v>
-      </c>
-      <c r="N351" t="n">
-        <v>16322391</v>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>43020236</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>16322391</t>
+        </is>
       </c>
       <c r="O351" t="inlineStr">
         <is>
@@ -22973,11 +24329,15 @@
       <c r="L352" t="n">
         <v>149</v>
       </c>
-      <c r="M352" t="n">
-        <v>51330337</v>
-      </c>
-      <c r="N352" t="n">
-        <v>21911106</v>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>51330337</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>21911106</t>
+        </is>
       </c>
       <c r="O352" t="inlineStr">
         <is>
@@ -23035,11 +24395,15 @@
       <c r="L353" t="n">
         <v>55</v>
       </c>
-      <c r="M353" t="n">
-        <v>373461399</v>
-      </c>
-      <c r="N353" t="n">
-        <v>28360612</v>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>373461399</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>28360612</t>
+        </is>
       </c>
       <c r="O353" t="inlineStr">
         <is>
@@ -23097,11 +24461,15 @@
       <c r="L354" t="n">
         <v>92</v>
       </c>
-      <c r="M354" t="n">
-        <v>372527342</v>
-      </c>
-      <c r="N354" t="n">
-        <v>24602301</v>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>372527342</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>24602301</t>
+        </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
@@ -23221,11 +24589,15 @@
       <c r="L356" t="n">
         <v>102</v>
       </c>
-      <c r="M356" t="n">
-        <v>2002799529</v>
-      </c>
-      <c r="N356" t="n">
-        <v>31615157</v>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>2002799529</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>31615157</t>
+        </is>
       </c>
       <c r="O356" t="inlineStr">
         <is>
@@ -23283,11 +24655,15 @@
       <c r="L357" t="n">
         <v>646</v>
       </c>
-      <c r="M357" t="n">
-        <v>46829130</v>
-      </c>
-      <c r="N357" t="n">
-        <v>17397839</v>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>46829130</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>17397839</t>
+        </is>
       </c>
       <c r="O357" t="inlineStr">
         <is>
@@ -23347,11 +24723,15 @@
       <c r="L358" t="n">
         <v>66</v>
       </c>
-      <c r="M358" t="n">
-        <v>617184310</v>
-      </c>
-      <c r="N358" t="n">
-        <v>28515051</v>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>617184310</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>28515051</t>
+        </is>
       </c>
       <c r="O358" t="inlineStr">
         <is>
@@ -23411,11 +24791,15 @@
       <c r="L359" t="n">
         <v>72</v>
       </c>
-      <c r="M359" t="n">
-        <v>2004445880</v>
-      </c>
-      <c r="N359" t="n">
-        <v>31877155</v>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>2004445880</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>31877155</t>
+        </is>
       </c>
       <c r="O359" t="inlineStr">
         <is>
@@ -23479,8 +24863,10 @@
       <c r="L360" t="n">
         <v>22</v>
       </c>
-      <c r="M360" t="n">
-        <v>2010910951</v>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>2010910951</t>
+        </is>
       </c>
       <c r="N360" t="inlineStr"/>
       <c r="O360" t="inlineStr">
@@ -23539,11 +24925,15 @@
       <c r="L361" t="n">
         <v>64</v>
       </c>
-      <c r="M361" t="n">
-        <v>52266180</v>
-      </c>
-      <c r="N361" t="n">
-        <v>23089571</v>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>52266180</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>23089571</t>
+        </is>
       </c>
       <c r="O361" t="inlineStr">
         <is>
@@ -23601,11 +24991,15 @@
       <c r="L362" t="n">
         <v>51</v>
       </c>
-      <c r="M362" t="n">
-        <v>635437062</v>
-      </c>
-      <c r="N362" t="n">
-        <v>34187051</v>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>635437062</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>34187051</t>
+        </is>
       </c>
       <c r="O362" t="inlineStr">
         <is>
@@ -23663,11 +25057,15 @@
       <c r="L363" t="n">
         <v>67</v>
       </c>
-      <c r="M363" t="n">
-        <v>2011933913</v>
-      </c>
-      <c r="N363" t="n">
-        <v>33794340</v>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>2011933913</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>33794340</t>
+        </is>
       </c>
       <c r="O363" t="inlineStr">
         <is>
@@ -23727,11 +25125,15 @@
       <c r="L364" t="n">
         <v>46</v>
       </c>
-      <c r="M364" t="n">
-        <v>2005957072</v>
-      </c>
-      <c r="N364" t="n">
-        <v>32152043</v>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2005957072</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>32152043</t>
+        </is>
       </c>
       <c r="O364" t="inlineStr">
         <is>
@@ -23796,8 +25198,10 @@
         <v>87</v>
       </c>
       <c r="M365" t="inlineStr"/>
-      <c r="N365" t="n">
-        <v>11824912</v>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>11824912</t>
+        </is>
       </c>
       <c r="O365" t="inlineStr">
         <is>
@@ -23857,11 +25261,15 @@
       <c r="L366" t="n">
         <v>131</v>
       </c>
-      <c r="M366" t="n">
-        <v>370530274</v>
-      </c>
-      <c r="N366" t="n">
-        <v>24341398</v>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>370530274</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>24341398</t>
+        </is>
       </c>
       <c r="O366" t="inlineStr">
         <is>
@@ -23919,11 +25327,15 @@
       <c r="L367" t="n">
         <v>53</v>
       </c>
-      <c r="M367" t="n">
-        <v>620222645</v>
-      </c>
-      <c r="N367" t="n">
-        <v>29136632</v>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>620222645</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>29136632</t>
+        </is>
       </c>
       <c r="O367" t="inlineStr">
         <is>
@@ -23986,8 +25398,10 @@
         <v>72</v>
       </c>
       <c r="M368" t="inlineStr"/>
-      <c r="N368" t="n">
-        <v>23961484</v>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>23961484</t>
+        </is>
       </c>
       <c r="O368" t="inlineStr">
         <is>
@@ -24045,11 +25459,15 @@
       <c r="L369" t="n">
         <v>38</v>
       </c>
-      <c r="M369" t="n">
-        <v>636863420</v>
-      </c>
-      <c r="N369" t="n">
-        <v>34878921</v>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>636863420</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>34878921</t>
+        </is>
       </c>
       <c r="O369" t="inlineStr">
         <is>
@@ -24107,11 +25525,15 @@
       <c r="L370" t="n">
         <v>171</v>
       </c>
-      <c r="M370" t="n">
-        <v>2001703172</v>
-      </c>
-      <c r="N370" t="n">
-        <v>30792154</v>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>2001703172</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>30792154</t>
+        </is>
       </c>
       <c r="O370" t="inlineStr">
         <is>
@@ -24169,11 +25591,15 @@
       <c r="L371" t="n">
         <v>252</v>
       </c>
-      <c r="M371" t="n">
-        <v>364771372</v>
-      </c>
-      <c r="N371" t="n">
-        <v>22419702</v>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>364771372</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>22419702</t>
+        </is>
       </c>
       <c r="O371" t="inlineStr">
         <is>
@@ -24231,11 +25657,15 @@
       <c r="L372" t="n">
         <v>100</v>
       </c>
-      <c r="M372" t="n">
-        <v>354383725</v>
-      </c>
-      <c r="N372" t="n">
-        <v>19708174</v>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>354383725</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>19708174</t>
+        </is>
       </c>
       <c r="O372" t="inlineStr">
         <is>
@@ -24291,11 +25721,15 @@
       <c r="L373" t="n">
         <v>87</v>
       </c>
-      <c r="M373" t="n">
-        <v>30154109</v>
-      </c>
-      <c r="N373" t="n">
-        <v>10731531</v>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>30154109</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>10731531</t>
+        </is>
       </c>
       <c r="O373" t="inlineStr">
         <is>
@@ -24349,8 +25783,10 @@
       </c>
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr"/>
-      <c r="M374" t="n">
-        <v>359164635</v>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>359164635</t>
+        </is>
       </c>
       <c r="N374" t="inlineStr"/>
       <c r="O374" t="inlineStr">
@@ -24407,11 +25843,15 @@
       <c r="L375" t="n">
         <v>61</v>
       </c>
-      <c r="M375" t="n">
-        <v>50208890</v>
-      </c>
-      <c r="N375" t="n">
-        <v>18635183</v>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>50208890</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>18635183</t>
+        </is>
       </c>
       <c r="O375" t="inlineStr">
         <is>
@@ -24471,11 +25911,15 @@
       <c r="L376" t="n">
         <v>39</v>
       </c>
-      <c r="M376" t="n">
-        <v>625532794</v>
-      </c>
-      <c r="N376" t="n">
-        <v>30123261</v>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>625532794</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>30123261</t>
+        </is>
       </c>
       <c r="O376" t="inlineStr">
         <is>
@@ -24533,8 +25977,10 @@
       </c>
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr"/>
-      <c r="M377" t="n">
-        <v>351182983</v>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>351182983</t>
+        </is>
       </c>
       <c r="N377" t="inlineStr"/>
       <c r="O377" t="inlineStr">
@@ -24595,11 +26041,15 @@
       <c r="L378" t="n">
         <v>87</v>
       </c>
-      <c r="M378" t="n">
-        <v>36583679</v>
-      </c>
-      <c r="N378" t="n">
-        <v>12734787</v>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>36583679</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>12734787</t>
+        </is>
       </c>
       <c r="O378" t="inlineStr">
         <is>
@@ -24660,11 +26110,15 @@
       <c r="L379" t="n">
         <v>90</v>
       </c>
-      <c r="M379" t="n">
-        <v>2015131879</v>
-      </c>
-      <c r="N379" t="n">
-        <v>34097062</v>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>2015131879</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>34097062</t>
+        </is>
       </c>
       <c r="O379" t="inlineStr">
         <is>
@@ -24724,11 +26178,15 @@
       <c r="L380" t="n">
         <v>122</v>
       </c>
-      <c r="M380" t="n">
-        <v>2018837749</v>
-      </c>
-      <c r="N380" t="n">
-        <v>35710599</v>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>2018837749</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>35710599</t>
+        </is>
       </c>
       <c r="O380" t="inlineStr">
         <is>
@@ -24788,11 +26246,15 @@
       <c r="L381" t="n">
         <v>103</v>
       </c>
-      <c r="M381" t="n">
-        <v>2011852670</v>
-      </c>
-      <c r="N381" t="n">
-        <v>32995892</v>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2011852670</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>32995892</t>
+        </is>
       </c>
       <c r="O381" t="inlineStr">
         <is>
@@ -24850,11 +26312,15 @@
       <c r="L382" t="n">
         <v>87</v>
       </c>
-      <c r="M382" t="n">
-        <v>2013973973</v>
-      </c>
-      <c r="N382" t="n">
-        <v>34665453</v>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>2013973973</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>34665453</t>
+        </is>
       </c>
       <c r="O382" t="inlineStr">
         <is>
@@ -24917,8 +26383,10 @@
       <c r="L383" t="n">
         <v>545</v>
       </c>
-      <c r="M383" t="n">
-        <v>29196593</v>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>29196593</t>
+        </is>
       </c>
       <c r="N383" t="inlineStr"/>
       <c r="O383" t="inlineStr">
@@ -24982,8 +26450,10 @@
       <c r="L384" t="n">
         <v>20</v>
       </c>
-      <c r="M384" t="n">
-        <v>2016672759</v>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2016672759</t>
+        </is>
       </c>
       <c r="N384" t="inlineStr"/>
       <c r="O384" t="inlineStr">
@@ -25040,11 +26510,15 @@
       </c>
       <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr"/>
-      <c r="M385" t="n">
-        <v>634512057</v>
-      </c>
-      <c r="N385" t="n">
-        <v>33683076</v>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>634512057</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>33683076</t>
+        </is>
       </c>
       <c r="O385" t="inlineStr">
         <is>
@@ -25102,11 +26576,15 @@
       <c r="L386" t="n">
         <v>41</v>
       </c>
-      <c r="M386" t="n">
-        <v>2010936482</v>
-      </c>
-      <c r="N386" t="n">
-        <v>33768489</v>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2010936482</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>33768489</t>
+        </is>
       </c>
       <c r="O386" t="inlineStr">
         <is>
@@ -25164,11 +26642,15 @@
       <c r="L387" t="n">
         <v>144</v>
       </c>
-      <c r="M387" t="n">
-        <v>40704940</v>
-      </c>
-      <c r="N387" t="n">
-        <v>15888157</v>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>40704940</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>15888157</t>
+        </is>
       </c>
       <c r="O387" t="inlineStr">
         <is>
@@ -25227,11 +26709,15 @@
       <c r="L388" t="n">
         <v>102</v>
       </c>
-      <c r="M388" t="n">
-        <v>2019458062</v>
-      </c>
-      <c r="N388" t="n">
-        <v>35554540</v>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>2019458062</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>35554540</t>
+        </is>
       </c>
       <c r="O388" t="inlineStr">
         <is>
@@ -25290,11 +26776,15 @@
       <c r="L389" t="n">
         <v>16</v>
       </c>
-      <c r="M389" t="n">
-        <v>634821038</v>
-      </c>
-      <c r="N389" t="n">
-        <v>33863670</v>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>634821038</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>33863670</t>
+        </is>
       </c>
       <c r="O389" t="inlineStr">
         <is>
@@ -25353,11 +26843,15 @@
       <c r="L390" t="n">
         <v>46</v>
       </c>
-      <c r="M390" t="n">
-        <v>2013555209</v>
-      </c>
-      <c r="N390" t="n">
-        <v>34152560</v>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>2013555209</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>34152560</t>
+        </is>
       </c>
       <c r="O390" t="inlineStr">
         <is>
@@ -25417,11 +26911,15 @@
       <c r="L391" t="n">
         <v>66</v>
       </c>
-      <c r="M391" t="n">
-        <v>626013667</v>
-      </c>
-      <c r="N391" t="n">
-        <v>30565716</v>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>626013667</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>30565716</t>
+        </is>
       </c>
       <c r="O391" t="inlineStr">
         <is>
@@ -25481,11 +26979,15 @@
       <c r="L392" t="n">
         <v>237</v>
       </c>
-      <c r="M392" t="n">
-        <v>34007478</v>
-      </c>
-      <c r="N392" t="n">
-        <v>11726582</v>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>34007478</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>11726582</t>
+        </is>
       </c>
       <c r="O392" t="inlineStr">
         <is>
@@ -25549,8 +27051,10 @@
       <c r="L393" t="n">
         <v>26</v>
       </c>
-      <c r="M393" t="n">
-        <v>52423932</v>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>52423932</t>
+        </is>
       </c>
       <c r="N393" t="inlineStr"/>
       <c r="O393" t="inlineStr">
